--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>1289.28</v>
+        <v>1373.54</v>
       </c>
     </row>
     <row r="4">
@@ -728,7 +728,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1042.03</v>
+        <v>1138.12</v>
       </c>
     </row>
     <row r="5">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>722.14</v>
+        <v>769.54</v>
       </c>
     </row>
     <row r="6">
@@ -845,7 +845,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -856,17 +856,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>551.6799999999999</v>
+        <v>584.26</v>
       </c>
     </row>
     <row r="8">
@@ -898,7 +898,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>529.28</v>
+        <v>554.0599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -993,7 +993,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>522.88</v>
+        <v>543.8099999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>480.85</v>
+        <v>498.19</v>
       </c>
     </row>
     <row r="11">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>462.27</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>442.85</v>
+        <v>465.99</v>
       </c>
     </row>
     <row r="13">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>427.37</v>
+        <v>460.44</v>
       </c>
     </row>
     <row r="14">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>427.09</v>
+        <v>451.53</v>
       </c>
     </row>
     <row r="15">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>415.73</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1333,17 +1333,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>407.3</v>
+        <v>436.47</v>
       </c>
     </row>
     <row r="17">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>404.75</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="18">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>364.64</v>
+        <v>373.76</v>
       </c>
     </row>
     <row r="19">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>353.52</v>
+        <v>373.71</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>341.92</v>
+        <v>356.44</v>
       </c>
     </row>
     <row r="21">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>309.56</v>
+        <v>346.04</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>280.56</v>
+        <v>300.37</v>
       </c>
     </row>
     <row r="23">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>272</v>
+        <v>281.48</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>267.16</v>
+        <v>269.07</v>
       </c>
     </row>
     <row r="25">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>261.71</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>256.24</v>
+        <v>267.16</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>246.41</v>
+        <v>261.64</v>
       </c>
     </row>
     <row r="28">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>245.21</v>
+        <v>253.25</v>
       </c>
     </row>
     <row r="29">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>241.97</v>
+        <v>245.47</v>
       </c>
     </row>
     <row r="30">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>234.84</v>
+        <v>240.97</v>
       </c>
     </row>
     <row r="31">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>222.23</v>
+        <v>231.43</v>
       </c>
     </row>
     <row r="32">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>213.3</v>
+        <v>227.99</v>
       </c>
     </row>
     <row r="33">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>189.17</v>
+        <v>218.96</v>
       </c>
     </row>
     <row r="34">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>184.64</v>
+        <v>203.16</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>179.72</v>
+        <v>203.06</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>178.09</v>
+        <v>198.3</v>
       </c>
     </row>
     <row r="37">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>175.62</v>
+        <v>195.81</v>
       </c>
     </row>
     <row r="38">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>168.02</v>
+        <v>191.65</v>
       </c>
     </row>
     <row r="39">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>167.16</v>
+        <v>181.85</v>
       </c>
     </row>
     <row r="40">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>159.45</v>
+        <v>179.72</v>
       </c>
     </row>
     <row r="41">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>158.95</v>
+        <v>166.34</v>
       </c>
     </row>
     <row r="42">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>156.02</v>
+        <v>162.28</v>
       </c>
     </row>
     <row r="43">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>134.77</v>
+        <v>139.02</v>
       </c>
     </row>
     <row r="44">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>133.93</v>
+        <v>138.72</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>132.33</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>131.29</v>
+        <v>132.33</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>122.41</v>
+        <v>131.29</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>113.02</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="49">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>104.47</v>
+        <v>125.96</v>
       </c>
     </row>
     <row r="50">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>100.93</v>
+        <v>117.26</v>
       </c>
     </row>
     <row r="51">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>99.01000000000001</v>
+        <v>114.44</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>98.08</v>
+        <v>107.81</v>
       </c>
     </row>
     <row r="53">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>97.44</v>
+        <v>105.52</v>
       </c>
     </row>
     <row r="54">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>96.44</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="55">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>93.93000000000001</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>93.13</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="57">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>92.5</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="58">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>86.77</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>85.16</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>84.7</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="61">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>83.84</v>
+        <v>87.41</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>78.84</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="63">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>77.40000000000001</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="64">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>74.67</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
+          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0579970825J</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>816290</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>73.66</v>
+        <v>80.27</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>70.43000000000001</v>
+        <v>78.68000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438112 - KIT4M0579970825J</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0579970825J</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816290</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>68.83</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>68.59</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>68.23999999999999</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>68.06999999999999</v>
+        <v>74.34</v>
       </c>
     </row>
     <row r="72">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>66.81</v>
+        <v>74.18000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>66.40000000000001</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>66.02</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>64.73999999999999</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>63.5</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>63.24</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>62.63</v>
+        <v>69.62</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799686CMX</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>816282</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>61.51</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>60.14</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438042 - KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05799686CMX</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816282</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>59.62</v>
+        <v>66.20999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>59.41</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>59.12</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>58.9</v>
+        <v>63.81</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>58.61</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>56.66</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>56.66</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>56.37</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>55.96</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>55.49</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>55.32</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,17 +5361,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>54.13</v>
+        <v>57.59</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>53.5</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,17 +5467,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>53.31</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>53.28</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>52.91</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>52.77</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>51.37</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>51.11</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>50.89</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="101">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>49.46</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>49.1</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>48.33</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>47.22</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>47.14</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="106">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>47.04</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>46.54</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>46.31</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="109">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>45.21</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="110">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>43.21</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>43.17</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="112">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>43.05</v>
+        <v>48</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>42.2</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>42.11</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>41.86</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>41.38</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,17 +6686,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>41.05</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>40.26</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>38.92</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>38.58</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,17 +6898,17 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>38.11</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>37.91</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799705T6B</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>816285</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>37.56</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>37.55</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="125">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438022 - KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05799705T6B</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>816285</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>36.41</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>35.85</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>35.67</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>35.23</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="129">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>32.92</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>32.79</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="131">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>32.57</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>32.09</v>
+        <v>36.42</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>31.96</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>31.89</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>31.31</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>30.43</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>29.63</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>28.85</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>28.71</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>28.61</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>27.77</v>
+        <v>30.35</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>27.68</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>27.31</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>26.95</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>26.93</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>26.33</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>25.48</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>25.19</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>25.16</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>25.06</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>25.04</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="152">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>24.85</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>24.76</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>24.37</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>23.99</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>23.45</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>22.87</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>22.46</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>22.39</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>21.97</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>21.59</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>21.49</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>21.21</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>21.17</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>21.16</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>21.1</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>20.96</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>20.16</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="170">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>19.99</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>19.94</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>19.92</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>19.66</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>19.63</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>19.52</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>19.38</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>19.13</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>19.01</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>18.91</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>18.56</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>18.55</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>17.71</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>17.31</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>16.04</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="185">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>15.78</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>15.76</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="187">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>15.56</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>15.51</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,17 +10502,17 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>15.31</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>15.08</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>14.6</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="192">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>14.02</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="193">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>13.84</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="194">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>13.57</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="195">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>13.28</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="196">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>13.14</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="197">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>12.64</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>12.44</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>12.19</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>11.58</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>11.03</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>10.74</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>10.71</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="204">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11297,17 +11297,17 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>10.66</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="205">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>10.07</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="206">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>9.25</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="207">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>9.130000000000001</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="208">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>8.48</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="209">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>7.74</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="210">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>7.51</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>7.48</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="212">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>6.34</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>5.99</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="214">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>5.92</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="215">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>5.53</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="216">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>5.49</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="217">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>5.39</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="218">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>4.49</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="219">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>4.08</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="220">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12145,12 +12145,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>2.93</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="221">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="222">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="223">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="224">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12357,17 +12357,17 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="225">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>1.22</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,17 +12463,17 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>1.13</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="227">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="228">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>0.85</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="229">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="230">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,17 +13046,17 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>809876</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,17 +13205,17 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,12 +13894,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16703,12 +16703,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16862,12 +16862,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16915,12 +16915,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17127,12 +17127,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17233,12 +17233,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17286,12 +17286,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17339,12 +17339,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17816,12 +17816,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17869,12 +17869,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17922,12 +17922,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17975,12 +17975,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18028,12 +18028,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18505,12 +18505,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,12 +19300,12 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19406,12 +19406,12 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,17 +19671,17 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H362" s="5" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
@@ -19724,12 +19724,12 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
@@ -19830,17 +19830,17 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G365" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H365" s="5" t="inlineStr">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -19883,12 +19883,12 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="G366" s="5" t="inlineStr">
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13 16:13 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-14 11:45 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14 11:45 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-15 08:09 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>1373.54</v>
+        <v>1466.75</v>
       </c>
     </row>
     <row r="4">
@@ -728,7 +728,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1138.12</v>
+        <v>1227.07</v>
       </c>
     </row>
     <row r="5">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>769.54</v>
+        <v>799.97</v>
       </c>
     </row>
     <row r="6">
@@ -792,7 +792,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -803,12 +803,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>638.87</v>
+        <v>642.1799999999999</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>584.26</v>
+        <v>638.87</v>
       </c>
     </row>
     <row r="8">
@@ -898,7 +898,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649192 - KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -909,17 +909,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>812924</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>554.0599999999999</v>
+        <v>573.1</v>
       </c>
     </row>
     <row r="9">
@@ -951,7 +951,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649192 - KIT4P00065641GDF</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -962,17 +962,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065641GDF</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>543.8099999999999</v>
+        <v>557.71</v>
       </c>
     </row>
     <row r="10">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>498.19</v>
+        <v>554.8099999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>480.85</v>
+        <v>513.85</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>465.99</v>
+        <v>484.68</v>
       </c>
     </row>
     <row r="13">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>460.44</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="14">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>451.53</v>
+        <v>466.53</v>
       </c>
     </row>
     <row r="15">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>449.99</v>
+        <v>463.33</v>
       </c>
     </row>
     <row r="16">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>436.47</v>
+        <v>451.76</v>
       </c>
     </row>
     <row r="17">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>373.76</v>
+        <v>396.56</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>373.71</v>
+        <v>383.8</v>
       </c>
     </row>
     <row r="20">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>356.44</v>
+        <v>382.41</v>
       </c>
     </row>
     <row r="21">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>346.04</v>
+        <v>348.01</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>300.37</v>
+        <v>315.83</v>
       </c>
     </row>
     <row r="23">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>281.48</v>
+        <v>299.73</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>269.07</v>
+        <v>283.95</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>268.91</v>
+        <v>280.06</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>267.16</v>
+        <v>278.05</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>261.64</v>
+        <v>270.88</v>
       </c>
     </row>
     <row r="28">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>253.25</v>
+        <v>267.16</v>
       </c>
     </row>
     <row r="29">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>245.47</v>
+        <v>258.98</v>
       </c>
     </row>
     <row r="30">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>240.97</v>
+        <v>252.83</v>
       </c>
     </row>
     <row r="31">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>231.43</v>
+        <v>251.13</v>
       </c>
     </row>
     <row r="32">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>227.99</v>
+        <v>247.04</v>
       </c>
     </row>
     <row r="33">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>218.96</v>
+        <v>233.01</v>
       </c>
     </row>
     <row r="34">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>203.16</v>
+        <v>227.56</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>203.06</v>
+        <v>213.31</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05799683GCK</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816270</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>198.3</v>
+        <v>210.31</v>
       </c>
     </row>
     <row r="37">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438032 - KIT4M05799683GCK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799683GCK</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>816270</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>195.81</v>
+        <v>205.75</v>
       </c>
     </row>
     <row r="38">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>191.65</v>
+        <v>200.72</v>
       </c>
     </row>
     <row r="39">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>181.85</v>
+        <v>193.29</v>
       </c>
     </row>
     <row r="40">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>166.34</v>
+        <v>179.24</v>
       </c>
     </row>
     <row r="42">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>162.28</v>
+        <v>171.74</v>
       </c>
     </row>
     <row r="43">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>139.02</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="44">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>138.72</v>
+        <v>165.28</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>134.81</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>132.33</v>
+        <v>144.21</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>131.29</v>
+        <v>134.84</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>129.99</v>
+        <v>132.33</v>
       </c>
     </row>
     <row r="49">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>125.96</v>
+        <v>131.29</v>
       </c>
     </row>
     <row r="50">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>117.26</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="51">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>114.44</v>
+        <v>126.94</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>107.81</v>
+        <v>125.22</v>
       </c>
     </row>
     <row r="53">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>105.52</v>
+        <v>122.96</v>
       </c>
     </row>
     <row r="54">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>103.46</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="55">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>100.93</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>99.86</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="57">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>97.44</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="58">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>96.98</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>96.33</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>92.52</v>
+        <v>100.74</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>87.41</v>
+        <v>100.04</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>87.19</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="63">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>84.53</v>
+        <v>96.86</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>83.56999999999999</v>
+        <v>89.45999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>80.43000000000001</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>80.27</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>78.68000000000001</v>
+        <v>88.34999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>78.2</v>
+        <v>87.53</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>76.8</v>
+        <v>87.45</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>86.48999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05799694RW2</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>816277</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>74.34</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438092 - KIT4M05799694RW2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799694RW2</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>816277</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>74.18000000000001</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>70.97</v>
+        <v>83.13</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>70.81</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>70.43000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="76">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>70.3</v>
+        <v>76.43000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>70.14</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>69.62</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>68.70999999999999</v>
+        <v>71.62</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>68.12</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="81">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>66.20999999999999</v>
+        <v>68.89</v>
       </c>
     </row>
     <row r="82">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>64.44</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>64.18000000000001</v>
+        <v>68.69</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,17 +4937,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>63.81</v>
+        <v>68.33</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>63.15</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>62.82</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>62.06</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>58.67</v>
+        <v>66.03</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>58.67</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>58.57</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>57.79</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>57.59</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>56.71</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>56.66</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>55.96</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,17 +5573,17 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>55.54</v>
+        <v>63.27</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>55.32</v>
+        <v>60.08</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>54.75</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>54.5</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>53.71</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>53.35</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799712SBX</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>816276</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>52.77</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>52.57</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="104">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>51.65</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05799701SGS</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816284</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>51.59</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438002 - KIT4M05799701SGS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799701SGS</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>816284</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>51.27</v>
+        <v>53.18</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438162 - KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05799712SBX</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>49.49</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>48.94</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>48.22</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="110">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>48.1</v>
+        <v>52.24</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>48.04</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="112">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>48</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>47.22</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="114">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>47.15</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>46.32</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>44.89</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>43.49</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>43.17</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>42.14</v>
+        <v>46.17</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>42.13</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>41.52</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="122">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>41.38</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>41.14</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>40.9</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="125">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>40.73</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>40.65</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>39.82</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,17 +7269,17 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>39.32</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>38.56</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>36.68</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="131">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>36.59</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>36.42</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05799706Z6R</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>816273</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>36.11</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>35.67</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="135">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>35.14</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>33.53</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>33.52</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437962 - KIT4M05799706Z6R</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799706Z6R</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>816273</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>33.32</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>31.96</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>31.31</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>30.35</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>29.38</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>29.06</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>28.85</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>28.84</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>28.71</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>28.61</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>28.39</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>27.93</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>27.77</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>27.68</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="152">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>27.14</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>26.61</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>26.38</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="155">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>26.32</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>24.76</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>23.97</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>23.6</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>23.34</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>23.18</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>22.53</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>22.46</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>22.39</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>21.97</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="165">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>21.77</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,17 +9283,17 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>21.73</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>21.59</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>21.47</v>
+        <v>24.73</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>21.4</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="170">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>21.36</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>21.21</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>21.17</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>21.14</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>21.12</v>
+        <v>23.29</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>20.89</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>20.44</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>20.36</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>20.03</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>19.94</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>19.63</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>19.42</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>18.55</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>18.38</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>18.03</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="185">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>17.9</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>16.69</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="187">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>16.35</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>15.76</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,17 +10502,17 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>15.73</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>15.56</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>15.31</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="192">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>14.89</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="193">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>14.75</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="194">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>14.67</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="195">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>14.6</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="196">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>14.27</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="197">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>13.84</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>13.3</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>13.22</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>12.91</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>12.53</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>12.44</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>12.19</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="204">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>12.19</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="205">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>11.38</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="206">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>10.95</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="207">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>10.71</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="208">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>10.07</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="209">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>9.25</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="210">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799732NQK</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816275</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>9.130000000000001</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="211">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437932 - KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05799732NQK</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816275</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>8.48</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>8.27</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>7.74</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="214">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>7.51</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="215">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>6.34</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="216">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>5.92</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="217">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>5.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="218">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>5.49</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="219">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>5.39</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="220">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12145,12 +12145,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>4.49</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="221">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>3.6</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="222">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>3.36</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="223">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>2.93</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="224">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>2.8</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="225">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12410,17 +12410,17 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>2.64</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,17 +12463,17 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>1.91</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="227">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="228">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>1.43</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="229">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.85</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="230">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="231">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12728,17 +12728,17 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="232">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12781,17 +12781,17 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="233">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12887,17 +12887,17 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="235">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,17 +12940,17 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="236">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,17 +13205,17 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799685DG5</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>816271</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,12 +13894,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438142  - KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799682BXX</t>
+          <t>KIT4M05799685DG5</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>816278</t>
+          <t>816271</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799676NNK</t>
+          <t>KIT4M05799682BXX</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816283</t>
+          <t>816278</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05799668SS7</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>816279</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438082 - KIT4M05799668SS7</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799668SS7</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816279</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438062 - KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05799676NNK</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816283</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,17 +14954,17 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15060,12 +15060,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17286,12 +17286,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17339,12 +17339,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17869,12 +17869,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18505,12 +18505,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,12 +19300,12 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F356" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G356" s="5" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
@@ -19406,12 +19406,12 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
@@ -19512,12 +19512,12 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -19618,12 +19618,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-15 08:09 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-15 08:11 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -20113,7 +20113,7 @@
     <row r="379">
       <c r="A379" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16 07:57 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-16 08:18 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16 22:39 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-16 22:40 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>1624.85</v>
+        <v>1650.84</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -644,12 +644,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>1493</v>
+        <v>1572.21</v>
       </c>
     </row>
     <row r="4">
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437292 - KIT4P000832806P4</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955062-KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -697,12 +697,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="7" t="n">
-        <v>1453.28</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="5">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>860.24</v>
+        <v>872.17</v>
       </c>
     </row>
     <row r="6">
@@ -834,7 +834,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>768.74</v>
+        <v>797.16</v>
       </c>
     </row>
     <row r="7">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>717.33</v>
+        <v>724.89</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>663.2</v>
+        <v>670.25</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>567.9</v>
+        <v>568.33</v>
       </c>
     </row>
     <row r="11">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>517.58</v>
+        <v>521.42</v>
       </c>
     </row>
     <row r="12">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>506.14</v>
+        <v>511.46</v>
       </c>
     </row>
     <row r="14">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>494.58</v>
+        <v>506.14</v>
       </c>
     </row>
     <row r="15">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>482</v>
+        <v>482.87</v>
       </c>
     </row>
     <row r="16">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>451.89</v>
+        <v>456.8</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>415.73</v>
+        <v>419.52</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>414.28</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="21">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>379.55</v>
+        <v>398.06</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>371.78</v>
+        <v>375.9</v>
       </c>
     </row>
     <row r="23">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>332.48</v>
+        <v>342.33</v>
       </c>
     </row>
     <row r="24">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>330.14</v>
+        <v>336.91</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>318.68</v>
+        <v>326.34</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>318.15</v>
+        <v>322.48</v>
       </c>
     </row>
     <row r="27">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>286.54</v>
+        <v>316.35</v>
       </c>
     </row>
     <row r="28">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>285.42</v>
+        <v>288.04</v>
       </c>
     </row>
     <row r="29">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>277.77</v>
+        <v>285.44</v>
       </c>
     </row>
     <row r="30">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>277.18</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="31">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>271.48</v>
+        <v>271.81</v>
       </c>
     </row>
     <row r="32">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>261.92</v>
+        <v>264.75</v>
       </c>
     </row>
     <row r="34">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>252.89</v>
+        <v>253.05</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>246.96</v>
+        <v>252.89</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>239.86</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="37">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>223.18</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="39">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>220.9</v>
+        <v>223.37</v>
       </c>
     </row>
     <row r="40">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>217.79</v>
+        <v>222.53</v>
       </c>
     </row>
     <row r="41">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>194.31</v>
+        <v>199.37</v>
       </c>
     </row>
     <row r="42">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>172.36</v>
+        <v>172.89</v>
       </c>
     </row>
     <row r="44">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>156.39</v>
+        <v>158.93</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>156.08</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>141.24</v>
+        <v>143.08</v>
       </c>
     </row>
     <row r="49">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,17 +3082,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>139</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="50">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>132.61</v>
+        <v>139.01</v>
       </c>
     </row>
     <row r="51">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>132.33</v>
+        <v>138.44</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>131.31</v>
+        <v>132.33</v>
       </c>
     </row>
     <row r="53">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="54">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3347,17 +3347,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>127.52</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="55">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>122.45</v>
+        <v>123.11</v>
       </c>
     </row>
     <row r="56">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>120.71</v>
+        <v>121.54</v>
       </c>
     </row>
     <row r="57">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>117.09</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="58">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>116.26</v>
+        <v>116.86</v>
       </c>
     </row>
     <row r="59">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>116.01</v>
+        <v>116.06</v>
       </c>
     </row>
     <row r="60">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>114.87</v>
+        <v>115.15</v>
       </c>
     </row>
     <row r="61">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>111.23</v>
+        <v>113.07</v>
       </c>
     </row>
     <row r="62">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>109.25</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="63">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>108.3</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="64">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>103.37</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>100.93</v>
+        <v>102.34</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>99.19</v>
+        <v>99.94</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>97.44</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>97.20999999999999</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>92.70999999999999</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>92.25</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>92.79000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>87.65000000000001</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>85.55</v>
+        <v>85.86</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>84.90000000000001</v>
+        <v>85.61</v>
       </c>
     </row>
     <row r="79">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>84.14</v>
+        <v>85.43000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>82.95999999999999</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>82.78</v>
+        <v>83.06999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>78.72</v>
+        <v>82.89</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>77.94</v>
+        <v>78.81</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>75.84</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>74.98</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="86">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>72.15000000000001</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>71.58</v>
+        <v>72.51000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>70.5</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>70.25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>66.95</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="94">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>66.77</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="95">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>66.53</v>
+        <v>67.12</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>65.58</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>65.37</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>65.05</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>64.84</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>63.76</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>61.94</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>61.33</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="103">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>59.07</v>
+        <v>60.24</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>58.17</v>
+        <v>59.14</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>57.21</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>55.96</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="107">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>52.92</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="110">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>51.43</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>51.43</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>50.65</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>50.44</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="117">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>49.81</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="118">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>49.27</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="119">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>48.75</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="120">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>48.23</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="121">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>48.13</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="122">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>48.06</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="123">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>46.96</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>46.52</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>46.52</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>46.1</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>46.04</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="130">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>44.48</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="131">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>44.27</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="132">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>44.15</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="133">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>42.07</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="134">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>39</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>38.09</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>38.01</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>36.41</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>36.33</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>35.99</v>
+        <v>36.78</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>35.98</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>35.97</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>35.9</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>35.71</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="144">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>34.03</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="147">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>33.92</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>33.8</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>33.75</v>
+        <v>34.11</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>33.71</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>33.47</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="152">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>33.38</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="153">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>32.76</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="154">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>32.31</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>31.86</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>31.24</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>31.15</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>30.65</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>29.59</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>29.28</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>29.12</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>28.85</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>28.74</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>28.72</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>27.87</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="167">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>26.7</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="168">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>26.52</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>26.09</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="170">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9495,17 +9495,17 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>26.03</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,17 +9548,17 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>25.41</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>24.19</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>23.74</v>
+        <v>24.21</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>23.67</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>23.63</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="176">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>21.24</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="180">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>19.51</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>18.8</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="187">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>18.46</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>17.38</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>17.26</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>16.74</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>16.7</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="192">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>12.48</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>12.31</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="200">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>10.94</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>10.75</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>10.67</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="204">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>8.119999999999999</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="210">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>6.94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16 22:40 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-17 07:31 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>1650.84</v>
+        <v>1754.52</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>1572.21</v>
+        <v>1690.35</v>
       </c>
     </row>
     <row r="4">
@@ -739,7 +739,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
+          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>872.17</v>
+        <v>914.01</v>
       </c>
     </row>
     <row r="6">
@@ -792,7 +792,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437282-KIT4P00084593R9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437252 - KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -803,12 +803,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>797.16</v>
+        <v>907.45</v>
       </c>
     </row>
     <row r="7">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>724.89</v>
+        <v>746.61</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>670.25</v>
+        <v>717.78</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>568.33</v>
+        <v>571.83</v>
       </c>
     </row>
     <row r="11">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>521.42</v>
+        <v>552.53</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>513.85</v>
+        <v>534.77</v>
       </c>
     </row>
     <row r="13">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>511.46</v>
+        <v>522.89</v>
       </c>
     </row>
     <row r="14">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>506.14</v>
+        <v>513.88</v>
       </c>
     </row>
     <row r="15">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>482.87</v>
+        <v>489.41</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>480.85</v>
+        <v>481.6</v>
       </c>
     </row>
     <row r="17">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>466.53</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="18">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>456.8</v>
+        <v>479.33</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>419.52</v>
+        <v>466.53</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>415.73</v>
+        <v>439.84</v>
       </c>
     </row>
     <row r="21">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>398.06</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>375.9</v>
+        <v>395.42</v>
       </c>
     </row>
     <row r="23">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>342.33</v>
+        <v>371.7</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>336.91</v>
+        <v>362.42</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>326.34</v>
+        <v>360.04</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>322.48</v>
+        <v>355.55</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>316.35</v>
+        <v>351.07</v>
       </c>
     </row>
     <row r="28">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>288.04</v>
+        <v>346.83</v>
       </c>
     </row>
     <row r="29">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>285.44</v>
+        <v>294.29</v>
       </c>
     </row>
     <row r="30">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>279.12</v>
+        <v>288.34</v>
       </c>
     </row>
     <row r="31">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>271.81</v>
+        <v>286.93</v>
       </c>
     </row>
     <row r="32">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>267.37</v>
+        <v>286.09</v>
       </c>
     </row>
     <row r="33">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>264.75</v>
+        <v>271.93</v>
       </c>
     </row>
     <row r="34">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>253.05</v>
+        <v>268.13</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>252.89</v>
+        <v>267.37</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>246.96</v>
+        <v>258.21</v>
       </c>
     </row>
     <row r="37">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>227.54</v>
+        <v>253.38</v>
       </c>
     </row>
     <row r="38">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>223.7</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="39">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>223.37</v>
+        <v>237.45</v>
       </c>
     </row>
     <row r="40">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>222.53</v>
+        <v>230.75</v>
       </c>
     </row>
     <row r="41">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>USPS - 05900510 - Los Angeles CA - CW6892232 - KIT4P00084601T5F</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>199.37</v>
+        <v>224.05</v>
       </c>
     </row>
     <row r="42">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>179.72</v>
+        <v>204.06</v>
       </c>
     </row>
     <row r="43">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>172.89</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="44">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>171.74</v>
+        <v>179.55</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>159.52</v>
+        <v>178.96</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>158.93</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>157.06</v>
+        <v>170.35</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>143.08</v>
+        <v>166.3</v>
       </c>
     </row>
     <row r="49">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,17 +3082,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>141.5</v>
+        <v>162.79</v>
       </c>
     </row>
     <row r="50">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>139.01</v>
+        <v>145.39</v>
       </c>
     </row>
     <row r="51">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>138.44</v>
+        <v>143.56</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>132.33</v>
+        <v>139.01</v>
       </c>
     </row>
     <row r="53">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>131.31</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="54">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>131.04</v>
+        <v>132.28</v>
       </c>
     </row>
     <row r="55">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>123.11</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>121.54</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="57">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>118.89</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="58">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>116.86</v>
+        <v>122.57</v>
       </c>
     </row>
     <row r="59">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>116.06</v>
+        <v>122.56</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>115.15</v>
+        <v>121.53</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>113.07</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>110.62</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="63">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>109.68</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>106.48</v>
+        <v>113.88</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>106.2</v>
+        <v>110.19</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>103.45</v>
+        <v>110.18</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>102.34</v>
+        <v>109.61</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>100.93</v>
+        <v>108.84</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>99.94</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>98.72</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>97.44</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>93.01000000000001</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>92.79000000000001</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>94.20999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>85.86</v>
+        <v>92.37</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>85.61</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>85.43000000000001</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>85.25</v>
+        <v>88.97</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>83.06999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="82">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>82.89</v>
+        <v>88.45999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>78.81</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>78.34</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>75.84</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,17 +5043,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>73.59</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="88">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>72.51000000000001</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>71.38</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,17 +5255,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>71.23999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>71</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>69.44</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>67.33</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>67.27</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>67.12</v>
+        <v>71.05</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>66.8</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>66.15000000000001</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>65.88</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>65.37</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>65.34999999999999</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>62.54</v>
+        <v>69.31999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>61.94</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>60.24</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>59.14</v>
+        <v>63.19</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>58.31</v>
+        <v>63.11</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>57.21</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>55.23</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>54.1</v>
+        <v>58.16</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>53.03</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="110">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>52.71</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>52.57</v>
+        <v>55.42</v>
       </c>
     </row>
     <row r="112">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>52.24</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>51.52</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>51.45</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>51.43</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>50.65</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>50.08</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>49.43</v>
+        <v>52.24</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,17 +6792,17 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>48.77</v>
+        <v>51.77</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>48.72</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>48.66</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>48.65</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>48.04</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>47.23</v>
+        <v>49.66</v>
       </c>
     </row>
     <row r="125">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>47.03</v>
+        <v>49.54</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>46.9</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>46.72</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>46.52</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>46.1</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>45.06</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>44.73</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>44.52</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>42.11</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>40.52</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>40.07</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>38.1</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="137">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>38.08</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>37.29</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>36.78</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="140">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>36.54</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>36.41</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>35.99</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>35.94</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>35.13</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>34.88</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>34.87</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>34.56</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>34.13</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>34.11</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="150">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>33.88</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>33.71</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="152">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>33.59</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="153">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>32.84</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>32.72</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>32.69</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>32.62</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>31.96</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>31.86</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>31.24</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>30.27</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>29.59</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>29.31</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>29.29</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>29.12</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>28.85</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>28.74</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>27.08</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>26.59</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>26.51</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="170">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>26.09</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,17 +9548,17 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>26.03</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,17 +9601,17 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>25.41</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>24.21</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>24.01</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="175">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>22.46</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>22.39</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>21.69</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>21.27</v>
+        <v>22.27</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>21.21</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>21.17</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>21.14</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>20.61</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>20.12</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="185">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>19.52</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>19.16</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="187">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>18.86</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>18.58</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>17.38</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="190">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>16.9</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>16.74</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="192">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>16.35</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="193">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>15.77</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="194">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>15.35</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="195">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>15.24</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="196">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>14.99</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="197">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>13.54</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>12.49</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>12.48</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>12.19</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>11.54</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>10.98</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>10.75</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="204">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>10.07</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="205">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>9.859999999999999</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="206">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11403,17 +11403,17 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>9.27</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>8.73</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="208">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>8.19</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="210">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="214">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="223">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="224">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="225">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12410,17 +12410,17 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,17 +12463,17 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="227">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12516,17 +12516,17 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="228">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="231">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="232">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12781,17 +12781,17 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="233">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="234">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12887,12 +12887,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="235">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,17 +12940,17 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="236">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,12 +13046,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,17 +13947,17 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14477,12 +14477,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15060,12 +15060,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809876</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,17 +19247,17 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H354" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,17 +19300,17 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-17 07:31 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-18 11:45 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>1754.52</v>
+        <v>1881.41</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>1690.35</v>
+        <v>1740.7</v>
       </c>
     </row>
     <row r="4">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>914.01</v>
+        <v>1107.35</v>
       </c>
     </row>
     <row r="6">
@@ -834,7 +834,7 @@
       </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="7" t="n">
-        <v>907.45</v>
+        <v>937.86</v>
       </c>
     </row>
     <row r="7">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>746.61</v>
+        <v>768.15</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>717.78</v>
+        <v>764.45</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>571.83</v>
+        <v>595.86</v>
       </c>
     </row>
     <row r="11">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>552.53</v>
+        <v>578.3</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>534.77</v>
+        <v>557.9299999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>522.89</v>
+        <v>550.5</v>
       </c>
     </row>
     <row r="14">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>513.88</v>
+        <v>544.47</v>
       </c>
     </row>
     <row r="15">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>489.41</v>
+        <v>513.88</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1333,17 +1333,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>481.6</v>
+        <v>502.83</v>
       </c>
     </row>
     <row r="17">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>480.85</v>
+        <v>500.45</v>
       </c>
     </row>
     <row r="18">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>479.33</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="19">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>439.84</v>
+        <v>451.76</v>
       </c>
     </row>
     <row r="21">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>415.73</v>
+        <v>428.62</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>395.42</v>
+        <v>418.02</v>
       </c>
     </row>
     <row r="23">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>371.7</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>362.42</v>
+        <v>394.25</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>360.04</v>
+        <v>384.64</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>355.55</v>
+        <v>382.14</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>351.07</v>
+        <v>381.62</v>
       </c>
     </row>
     <row r="28">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>346.83</v>
+        <v>380.12</v>
       </c>
     </row>
     <row r="29">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>294.29</v>
+        <v>355.04</v>
       </c>
     </row>
     <row r="30">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>288.34</v>
+        <v>320.55</v>
       </c>
     </row>
     <row r="31">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>286.93</v>
+        <v>294.15</v>
       </c>
     </row>
     <row r="32">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>286.09</v>
+        <v>291.45</v>
       </c>
     </row>
     <row r="33">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>271.93</v>
+        <v>290.09</v>
       </c>
     </row>
     <row r="34">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>268.13</v>
+        <v>272.04</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>267.37</v>
+        <v>271.17</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>258.21</v>
+        <v>267.37</v>
       </c>
     </row>
     <row r="37">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>253.38</v>
+        <v>257.85</v>
       </c>
     </row>
     <row r="38">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>246.96</v>
+        <v>254.04</v>
       </c>
     </row>
     <row r="39">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>237.45</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="40">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>230.75</v>
+        <v>241.16</v>
       </c>
     </row>
     <row r="41">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>224.05</v>
+        <v>237.44</v>
       </c>
     </row>
     <row r="42">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>204.06</v>
+        <v>233.48</v>
       </c>
     </row>
     <row r="43">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>180.28</v>
+        <v>196.18</v>
       </c>
     </row>
     <row r="44">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>179.55</v>
+        <v>183.36</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>178.96</v>
+        <v>183.21</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>175.96</v>
+        <v>181.73</v>
       </c>
     </row>
     <row r="47">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>170.35</v>
+        <v>181.72</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>166.3</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="49">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,17 +3082,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>162.79</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="50">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>145.39</v>
+        <v>160.96</v>
       </c>
     </row>
     <row r="51">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>143.56</v>
+        <v>153.25</v>
       </c>
     </row>
     <row r="52">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>139.01</v>
+        <v>152.17</v>
       </c>
     </row>
     <row r="53">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>132.39</v>
+        <v>144.92</v>
       </c>
     </row>
     <row r="54">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>132.28</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="55">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>131.31</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="57">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>126.03</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="58">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>122.57</v>
+        <v>128.34</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>122.56</v>
+        <v>127.51</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>121.53</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>119.92</v>
+        <v>124.08</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>118.35</v>
+        <v>123.56</v>
       </c>
     </row>
     <row r="63">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>116.15</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>113.88</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>110.19</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>110.18</v>
+        <v>119.32</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>109.61</v>
+        <v>116.74</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>108.84</v>
+        <v>113.93</v>
       </c>
     </row>
     <row r="69">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>106.53</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>106.48</v>
+        <v>107.32</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>100.93</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>99.61</v>
+        <v>102.79</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>97.44</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>94.92</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>94.20999999999999</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>92.37</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>90.15000000000001</v>
+        <v>96.23999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>88.97</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>88.8</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="82">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>88.45999999999999</v>
+        <v>91.19</v>
       </c>
     </row>
     <row r="83">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>88.17</v>
+        <v>90.53</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>80.36</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>78.63</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>75.84</v>
+        <v>82.19</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>75.01000000000001</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>73.90000000000001</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>73.68000000000001</v>
+        <v>76.37</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>73.05</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>72.73</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>71.38</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>71.05</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="96">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>70.89</v>
+        <v>75.13</v>
       </c>
     </row>
     <row r="97">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>70.66</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>70.5</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,17 +5732,17 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>69.88</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>69.44</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>69.31999999999999</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>66.09999999999999</v>
+        <v>71.36</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>63.51</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="104">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>63.19</v>
+        <v>68.43000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>63.11</v>
+        <v>67.20999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>62.58</v>
+        <v>66.62</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>61.53</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>58.16</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>57.63</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="110">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>56.05</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>55.42</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="112">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>55.18</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>54.15</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>54.05</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>53.99</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>53.93</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>52.57</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>52.24</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="119">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>51.77</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>51.65</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>51.48</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>51.43</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>49.9</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>49.66</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="125">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>49.43</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>48.98</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>48.75</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>48.04</v>
+        <v>52.14</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>47.23</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>46.89</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>46.78</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>46.66</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>46.52</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>46.1</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>45.67</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>44.71</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>42.77</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>40.77</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>40.45</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>39.41</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>39.35</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="143">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>39.25</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>38.45</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>38.05</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="146">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>37.8</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>37.7</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>37.27</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="149">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>37.22</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="150">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>37.2</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>36.48</v>
+        <v>39.47</v>
       </c>
     </row>
     <row r="152">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>35.99</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>35.69</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>35.29</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>35.23</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>35.09</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>34.66</v>
+        <v>36.55</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>34.5</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>32.55</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>32.5</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>32.13</v>
+        <v>35.58</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>32.09</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>31.51</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>31.24</v>
+        <v>31.73</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>29.31</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>29.26</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>29.25</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>28.85</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>28.74</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="170">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>27.76</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="171">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>27.48</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="172">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,17 +9654,17 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>25.13</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>24.26</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>23.74</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>22.85</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>22.46</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>22.39</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>22.27</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>22.13</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>21.69</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>21.21</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>21.17</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>20.88</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="185">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>20.88</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>20.61</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="187">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>20.24</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>20.12</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>19.65</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>18.16</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>17.57</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="192">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>17.49</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="193">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>17.45</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="194">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>16.47</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="195">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>16.01</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="196">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>15.77</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="197">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>15.4</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>15.35</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>13.54</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>13.22</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>12.48</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,17 +11191,17 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>12.3</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>12.19</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="204">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>10.75</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="205">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>10.07</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="206">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11403,17 +11403,17 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>9.869999999999999</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="207">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>9.27</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="208">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>8.529999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="209">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>8.25</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="210">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>7.91</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>7.74</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="212">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>7.52</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>7.35</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="214">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>5.53</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="215">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>5.39</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="216">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>4.49</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="217">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>3.06</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="218">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>2.93</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="219">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="220">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12145,12 +12145,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="221">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>0.85</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="222">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>0.39</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="223">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>0.33</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="224">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12357,17 +12357,17 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>0.26</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="225">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>0.12</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,17 +12463,17 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.06</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="227">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.05</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="228">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>0.04</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="229">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12622,17 +12622,17 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="230">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="231">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12728,17 +12728,17 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="232">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12781,12 +12781,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="233">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="234">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12887,12 +12887,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="7" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="235">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,17 +12940,17 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="236">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="237">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,12 +13046,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="L237" s="5" t="n"/>
       <c r="M237" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="238">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="L238" s="5" t="n"/>
       <c r="M238" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="239">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,12 +13894,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,17 +13947,17 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15060,12 +15060,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16703,12 +16703,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16862,12 +16862,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16915,12 +16915,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17127,12 +17127,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17233,12 +17233,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17286,12 +17286,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17339,12 +17339,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17816,12 +17816,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17922,12 +17922,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17975,12 +17975,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18028,12 +18028,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18505,12 +18505,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649802 - KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>809876</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649742 - KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
@@ -19300,12 +19300,12 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-18 11:45 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-19 13:36 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>1881.41</v>
+        <v>1990.98</v>
       </c>
     </row>
     <row r="3">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1107.35</v>
+        <v>1183.33</v>
       </c>
     </row>
     <row r="6">
@@ -845,7 +845,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649192 - KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>812924</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>768.15</v>
+        <v>830.67</v>
       </c>
     </row>
     <row r="8">
@@ -898,7 +898,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649192 - KIT4P00065641GDF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -909,12 +909,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065641GDF</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>764.45</v>
+        <v>771.66</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>595.86</v>
+        <v>621.25</v>
       </c>
     </row>
     <row r="11">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>578.3</v>
+        <v>619.12</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>557.9299999999999</v>
+        <v>581.65</v>
       </c>
     </row>
     <row r="13">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>550.5</v>
+        <v>567.46</v>
       </c>
     </row>
     <row r="14">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>544.47</v>
+        <v>547.95</v>
       </c>
     </row>
     <row r="15">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>502.83</v>
+        <v>509.1</v>
       </c>
     </row>
     <row r="17">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>466.53</v>
+        <v>467.07</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>451.76</v>
+        <v>466.53</v>
       </c>
     </row>
     <row r="21">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>428.62</v>
+        <v>457.57</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>418.02</v>
+        <v>441.54</v>
       </c>
     </row>
     <row r="23">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>415.73</v>
+        <v>437.08</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>394.25</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>384.64</v>
+        <v>409.47</v>
       </c>
     </row>
     <row r="26">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>382.14</v>
+        <v>408.28</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>381.62</v>
+        <v>401.42</v>
       </c>
     </row>
     <row r="28">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>380.12</v>
+        <v>391.75</v>
       </c>
     </row>
     <row r="29">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>355.04</v>
+        <v>387.05</v>
       </c>
     </row>
     <row r="30">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>320.55</v>
+        <v>320.99</v>
       </c>
     </row>
     <row r="31">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>294.15</v>
+        <v>318.95</v>
       </c>
     </row>
     <row r="32">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>291.45</v>
+        <v>306.49</v>
       </c>
     </row>
     <row r="33">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>290.09</v>
+        <v>292.72</v>
       </c>
     </row>
     <row r="34">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>272.04</v>
+        <v>285.93</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649592 - KIT4M05413787HHK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>271.17</v>
+        <v>272.25</v>
       </c>
     </row>
     <row r="36">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>257.85</v>
+        <v>266.3</v>
       </c>
     </row>
     <row r="38">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>254.04</v>
+        <v>255.25</v>
       </c>
     </row>
     <row r="39">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>241.16</v>
+        <v>246.41</v>
       </c>
     </row>
     <row r="41">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>237.44</v>
+        <v>244.3</v>
       </c>
     </row>
     <row r="42">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>233.48</v>
+        <v>241.16</v>
       </c>
     </row>
     <row r="43">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>196.18</v>
+        <v>237.44</v>
       </c>
     </row>
     <row r="44">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>183.36</v>
+        <v>204.14</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>183.21</v>
+        <v>188.94</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>181.73</v>
+        <v>188.58</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>181.72</v>
+        <v>185.64</v>
       </c>
     </row>
     <row r="48">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>169.8</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="50">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>160.96</v>
+        <v>176.14</v>
       </c>
     </row>
     <row r="51">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>153.25</v>
+        <v>160.14</v>
       </c>
     </row>
     <row r="52">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>152.17</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="53">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>144.92</v>
+        <v>145.95</v>
       </c>
     </row>
     <row r="54">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>134.88</v>
+        <v>143.48</v>
       </c>
     </row>
     <row r="55">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>132.39</v>
+        <v>139.56</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>131.31</v>
+        <v>137.54</v>
       </c>
     </row>
     <row r="57">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>131.04</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="58">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>128.34</v>
+        <v>131.37</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>127.51</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>126.03</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>124.08</v>
+        <v>129.55</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>123.56</v>
+        <v>127.14</v>
       </c>
     </row>
     <row r="63">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>123.4</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>122.24</v>
+        <v>125.01</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>119.92</v>
+        <v>124.38</v>
       </c>
     </row>
     <row r="66">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>119.32</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>116.74</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>113.93</v>
+        <v>119.79</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>109.26</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>107.32</v>
+        <v>112.93</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>106.48</v>
+        <v>108.43</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>103.5</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>102.79</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>102.53</v>
+        <v>104.12</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>100.93</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>97.44</v>
+        <v>100.79</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>96.23999999999999</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>94.33</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>93.20999999999999</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>91.45</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="82">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>91.19</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>90.53</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>91.47</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>84.13</v>
+        <v>91.03</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>82.19</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>80.31</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>79.23</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>77.45</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>76.37</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>75.84</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>75.81</v>
+        <v>80.33</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>75.69</v>
+        <v>79.39</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>75.2</v>
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>75.13</v>
+        <v>77.45999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>74.98</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>74.76000000000001</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,17 +5732,17 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>71.76000000000001</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>71.38</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>71.36</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>69.44</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>68.43000000000001</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>67.20999999999999</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>66.62</v>
+        <v>71.42</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>64.33</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>62.59</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>62.58</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>61.72</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>61.51</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="112">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>59.91</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>58.93</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>58.76</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>58.41</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>57.9</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>55.94</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>55.84</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,17 +6792,17 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>54.82</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>54.68</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>54.45</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,17 +6951,17 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>54.25</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>53.95</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>53.47</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="125">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>52.75</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>52.58</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>52.57</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>52.49</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>52.14</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>52.12</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>51.52</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>50.59</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>49.93</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="134">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>48.75</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>48.04</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>47.23</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>46.14</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>46.1</v>
+        <v>51.23</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>45.68</v>
+        <v>50.42</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>45.24</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>44.95</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>43.96</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>43.08</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>42.77</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>41.65</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>41.28</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>40.11</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>40.08</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>39.99</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>39.75</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>39.47</v>
+        <v>43.41</v>
       </c>
     </row>
     <row r="152">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>39.41</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>38.88</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>37.89</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>37.16</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>36.92</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>36.55</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>36.48</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>36.1</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>35.99</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>35.58</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>32.29</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="163">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>32.09</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>31.73</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>31.24</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>29.7</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>29.31</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>29.27</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>28.85</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="170">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>28.63</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>28.42</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,17 +9601,17 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>26.15</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,17 +9654,17 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>26.04</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>25.79</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,17 +9760,17 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>25.21</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>24.74</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>24.55</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>23.74</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>23.46</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>22.47</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>22.39</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>22.3</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>22.18</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>21.69</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="185">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>21.21</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="187">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>21.17</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>20.88</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>20.61</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>20.12</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>19.65</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="192">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>19.28</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="193">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>17.62</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="194">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>17.57</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="195">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>17.49</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="196">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>17.45</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="197">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>16.78</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>15.91</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>15.77</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>15.35</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>13.98</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="202">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>13.65</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="203">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>13.54</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="204">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>12.48</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="205">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>12.19</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="206">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>10.75</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="207">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>10.07</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="208">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>9.85</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="209">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>9.27</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="210">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="211">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>8.35</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="212">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>7.91</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>7.74</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>7.52</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="215">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>6.53</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="216">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>5.53</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="217">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>5.46</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="218">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>4.49</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="219">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>2.93</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="220">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12145,12 +12145,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>2.8</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="221">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649722 - KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="7" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="222">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6642812 - KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="7" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="223">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437732 - KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="7" t="n">
-        <v>1.12</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="224">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>0.85</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="225">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>0.85</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="227">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12516,17 +12516,17 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.39</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="228">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12569,17 +12569,17 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="229">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12622,17 +12622,17 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="230">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12675,17 +12675,17 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="231">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12728,17 +12728,17 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="232">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12781,17 +12781,17 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="233">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="236">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="237">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,12 +13046,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,17 +13152,17 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="240">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,17 +13682,17 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,12 +13894,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14477,12 +14477,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15060,12 +15060,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437632 - KIT4M05872585HZZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16703,12 +16703,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16862,12 +16862,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16915,12 +16915,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17127,12 +17127,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17233,12 +17233,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17286,12 +17286,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17339,12 +17339,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491825PF9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
@@ -17710,12 +17710,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491824JCK</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918239TM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -17816,12 +17816,12 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491822SF6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17922,12 +17922,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
@@ -17975,12 +17975,12 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918197VX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
@@ -18028,12 +18028,12 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491817T79</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918154FM</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18505,12 +18505,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 13:36 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 08:43 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 08:43 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 09:45 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 09:45 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 09:47 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 09:47 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 09:55 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 09:55 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 09:58 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 09:58 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 10:06 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 10:06 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 10:08 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 10:08 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 10:21 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 10:21 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 10:25 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 10:25 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 10:27 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 10:27 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 12:15 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 12:15 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 12:19 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>1990.98</v>
+        <v>2003.09</v>
       </c>
     </row>
     <row r="3">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1183.33</v>
+        <v>1208.24</v>
       </c>
     </row>
     <row r="6">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>830.67</v>
+        <v>834.51</v>
       </c>
     </row>
     <row r="8">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>621.25</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="11">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>619.12</v>
+        <v>621.59</v>
       </c>
     </row>
     <row r="12">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>581.65</v>
+        <v>581.8200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>567.46</v>
+        <v>567.51</v>
       </c>
     </row>
     <row r="14">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>547.95</v>
+        <v>548.64</v>
       </c>
     </row>
     <row r="15">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>509.1</v>
+        <v>509.65</v>
       </c>
     </row>
     <row r="17">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>467.07</v>
+        <v>468.1</v>
       </c>
     </row>
     <row r="20">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>457.57</v>
+        <v>461.4</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>441.54</v>
+        <v>442.55</v>
       </c>
     </row>
     <row r="23">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>437.08</v>
+        <v>441.51</v>
       </c>
     </row>
     <row r="24">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>409.47</v>
+        <v>411.14</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>408.28</v>
+        <v>410.32</v>
       </c>
     </row>
     <row r="27">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>401.42</v>
+        <v>401.89</v>
       </c>
     </row>
     <row r="28">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>391.75</v>
+        <v>394.48</v>
       </c>
     </row>
     <row r="29">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>387.05</v>
+        <v>391.27</v>
       </c>
     </row>
     <row r="30">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>320.99</v>
+        <v>322.82</v>
       </c>
     </row>
     <row r="31">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955502 - KIT4M05563502GJS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>318.95</v>
+        <v>321.03</v>
       </c>
     </row>
     <row r="32">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>306.49</v>
+        <v>306.77</v>
       </c>
     </row>
     <row r="33">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>292.72</v>
+        <v>293.49</v>
       </c>
     </row>
     <row r="34">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>285.93</v>
+        <v>287.87</v>
       </c>
     </row>
     <row r="35">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>266.3</v>
+        <v>266.68</v>
       </c>
     </row>
     <row r="38">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>246.96</v>
+        <v>247.81</v>
       </c>
     </row>
     <row r="40">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>246.41</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="41">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>244.3</v>
+        <v>244.62</v>
       </c>
     </row>
     <row r="42">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>204.14</v>
+        <v>205.74</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>188.94</v>
+        <v>189.97</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>188.58</v>
+        <v>188.94</v>
       </c>
     </row>
     <row r="47">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>185.64</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>178.66</v>
+        <v>178.97</v>
       </c>
     </row>
     <row r="50">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>176.14</v>
+        <v>176.99</v>
       </c>
     </row>
     <row r="51">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>160.14</v>
+        <v>161.35</v>
       </c>
     </row>
     <row r="52">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>154.26</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="53">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>143.48</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="55">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>132.39</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="58">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>131.37</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="59">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>129.55</v>
+        <v>130.19</v>
       </c>
     </row>
     <row r="62">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>127.14</v>
+        <v>127.52</v>
       </c>
     </row>
     <row r="63">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>125.01</v>
+        <v>125.07</v>
       </c>
     </row>
     <row r="65">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>120.06</v>
+        <v>120.67</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>119.92</v>
+        <v>120.14</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>119.79</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="69">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>117.7</v>
+        <v>118.19</v>
       </c>
     </row>
     <row r="70">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>108.43</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="72">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>107.2</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="73">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>102.89</v>
+        <v>103.03</v>
       </c>
     </row>
     <row r="76">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>100.79</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>100.62</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>98.28</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>97.56</v>
+        <v>97.78</v>
       </c>
     </row>
     <row r="81">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>96.47</v>
+        <v>96.52</v>
       </c>
     </row>
     <row r="83">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>93.73</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="84">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>91.47</v>
+        <v>93.05</v>
       </c>
     </row>
     <row r="86">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>80.33</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>79.39</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>77.56999999999999</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>76.48999999999999</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>73.89</v>
+        <v>74.19</v>
       </c>
     </row>
     <row r="105">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>71.42</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>71.38</v>
+        <v>71.42</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>70.8</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="109">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>67.59999999999999</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="110">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>66.75</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>63.83</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="113">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>63.05</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="114">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,17 +6580,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>62.33</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>59.66</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>59.22</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>59.02</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>58.6</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="120">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>58.31</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="121">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>56.71</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="123">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>56.33</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="125">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>53.19</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>53.13</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="132">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>52.57</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>52.5</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="135">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>52.33</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="136">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>51.3</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="138">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>51.23</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="139">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>50.42</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="140">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>47.86</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="142">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>44.43</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="149">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>44.35</v>
+        <v>44.41</v>
       </c>
     </row>
     <row r="150">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>43.9</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="151">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>43.41</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="152">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>42.61</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>42.45</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="154">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>40.32</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="155">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>39.17</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="157">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>37.87</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="159">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>37.7</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="160">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>35.6</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>34.05</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>33.39</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>32.22</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>31.85</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="168">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>29.87</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="170">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>29.59</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="171">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>25.33</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>25.21</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>24.34</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>23.97</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>23.85</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="183">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>21.21</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>20.88</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="192">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>18.06</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="196">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>14.77</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="203">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>14.68</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="204">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>10.07</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="209">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>9.85</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="210">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>9.27</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="211">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>8.67</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>8.59</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="213">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="218">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="221">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 12:19 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 12:29 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 12:29 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-20 12:30 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2003.09</v>
+        <v>2099.05</v>
       </c>
     </row>
     <row r="3">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1208.24</v>
+        <v>1332.43</v>
       </c>
     </row>
     <row r="6">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>834.51</v>
+        <v>878.66</v>
       </c>
     </row>
     <row r="8">
@@ -951,7 +951,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -962,12 +962,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>638.87</v>
+        <v>754.4</v>
       </c>
     </row>
     <row r="10">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>630.49</v>
+        <v>643.48</v>
       </c>
     </row>
     <row r="11">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650122-KIT4M05413776H84</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955042 - KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="7" t="n">
-        <v>621.59</v>
+        <v>638.87</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>581.8200000000001</v>
+        <v>585.9299999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955452-KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>567.51</v>
+        <v>583.4400000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649792 - KIT4M04475151HTP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955082 - KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>548.64</v>
+        <v>569.74</v>
       </c>
     </row>
     <row r="15">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>513.88</v>
+        <v>518.0700000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>509.65</v>
+        <v>513.88</v>
       </c>
     </row>
     <row r="17">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>480.85</v>
+        <v>496.26</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>468.1</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>466.53</v>
+        <v>475.35</v>
       </c>
     </row>
     <row r="21">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1598,17 +1598,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>461.4</v>
+        <v>473.96</v>
       </c>
     </row>
     <row r="22">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>442.55</v>
+        <v>466.53</v>
       </c>
     </row>
     <row r="23">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649632 - KIT4M054138064J9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>441.51</v>
+        <v>450.18</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>415.73</v>
+        <v>428.89</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>411.14</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="26">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>410.32</v>
+        <v>410.85</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SMAR-05900510-Los Angeles CA-020426442-KIT4P00065630DZT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>401.89</v>
+        <v>410.4</v>
       </c>
     </row>
     <row r="28">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>394.48</v>
+        <v>408.48</v>
       </c>
     </row>
     <row r="29">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="7" t="n">
-        <v>391.27</v>
+        <v>401.51</v>
       </c>
     </row>
     <row r="30">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>322.82</v>
+        <v>341.85</v>
       </c>
     </row>
     <row r="31">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>321.03</v>
+        <v>321.84</v>
       </c>
     </row>
     <row r="32">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>306.77</v>
+        <v>313.55</v>
       </c>
     </row>
     <row r="33">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>293.49</v>
+        <v>298.99</v>
       </c>
     </row>
     <row r="34">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>287.87</v>
+        <v>298.15</v>
       </c>
     </row>
     <row r="35">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649252 - KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>272.25</v>
+        <v>297.09</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>267.37</v>
+        <v>272.98</v>
       </c>
     </row>
     <row r="37">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>266.68</v>
+        <v>267.37</v>
       </c>
     </row>
     <row r="38">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SMRT-05900510-Los Angeles CA-020649182-KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>255.25</v>
+        <v>266.95</v>
       </c>
     </row>
     <row r="39">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>247.81</v>
+        <v>257.01</v>
       </c>
     </row>
     <row r="40">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>246.96</v>
+        <v>256.73</v>
       </c>
     </row>
     <row r="41">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>244.62</v>
+        <v>249.72</v>
       </c>
     </row>
     <row r="42">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649542 - KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="7" t="n">
-        <v>241.16</v>
+        <v>246.96</v>
       </c>
     </row>
     <row r="43">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
+          <t>SMRT-05900510-Los Angeles CA-021437812-KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="7" t="n">
-        <v>237.44</v>
+        <v>241.16</v>
       </c>
     </row>
     <row r="44">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827012 - KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="7" t="n">
-        <v>205.74</v>
+        <v>237.44</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>189.97</v>
+        <v>198.69</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>188.94</v>
+        <v>198.15</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>186</v>
+        <v>196.77</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>180.28</v>
+        <v>187.68</v>
       </c>
     </row>
     <row r="49">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>178.97</v>
+        <v>182.67</v>
       </c>
     </row>
     <row r="50">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437672 - KIT4M05872531DSZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>176.99</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="51">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>161.35</v>
+        <v>172.83</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>154.85</v>
+        <v>172.31</v>
       </c>
     </row>
     <row r="53">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649232 - KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>145.95</v>
+        <v>168.97</v>
       </c>
     </row>
     <row r="54">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="7" t="n">
-        <v>143.75</v>
+        <v>158.82</v>
       </c>
     </row>
     <row r="55">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955532 - KIT4M05563548P9Q</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>139.56</v>
+        <v>146.99</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>137.54</v>
+        <v>144.89</v>
       </c>
     </row>
     <row r="57">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>133.09</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="58">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>132.39</v>
+        <v>137.76</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>131.31</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>130.19</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>127.52</v>
+        <v>130.94</v>
       </c>
     </row>
     <row r="63">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>126.03</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>125.07</v>
+        <v>129.82</v>
       </c>
     </row>
     <row r="65">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>124.38</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>120.67</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>120.14</v>
+        <v>123.21</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>119.92</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>118.19</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>112.93</v>
+        <v>119.07</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>108.45</v>
+        <v>117.68</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>107.57</v>
+        <v>117.09</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>106.48</v>
+        <v>115.85</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>104.12</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>103.03</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>100.93</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>100.8</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>100.62</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>104.21</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>97.78</v>
+        <v>101.98</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>97.44</v>
+        <v>101.97</v>
       </c>
     </row>
     <row r="82">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>96.52</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>94.52</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>93.20999999999999</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>93.05</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>91.03</v>
+        <v>95.48999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>89.48999999999999</v>
+        <v>92.09</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>87.73</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>80.98</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,17 +5361,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>80.93000000000001</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>80.48999999999999</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>79.43000000000001</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>77.59999999999999</v>
+        <v>85.23</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>77.45999999999999</v>
+        <v>85.20999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>76.90000000000001</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>75.84</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>75.84</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>75.81</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>75.61</v>
+        <v>79.13</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>74.76000000000001</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>74.19</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>72.23999999999999</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>72.06</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>71.42</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,17 +6209,17 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>71.38</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>67.95</v>
+        <v>74.54000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>66.90000000000001</v>
+        <v>72.27</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>64.33</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="112">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>63.95</v>
+        <v>70.06</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>63.13</v>
+        <v>69.31999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>62.58</v>
+        <v>66.93000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,17 +6580,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>62.39</v>
+        <v>65.39</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>62.38</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>59.47</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>59.34</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>59.22</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>58.57</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>57.98</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,17 +6951,17 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>57.22</v>
+        <v>59.04</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>56.5</v>
+        <v>58.42</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>56.34</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="125">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>55.94</v>
+        <v>57.66</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>54.46</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>54.18</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>53.95</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>53.59</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>53.2</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>53.19</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>53.11</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="133">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>52.6</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>52.57</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>52.12</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>51.69</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>51.26</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>50.45</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>48.04</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>47.92</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>47.23</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>46.57</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="144">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>46.37</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>46.1</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>45.68</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="147">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>44.95</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>44.44</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>44.41</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>44.27</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>43.43</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="152">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>42.86</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>42.63</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>40.33</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>39.41</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="156">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>39.27</v>
+        <v>41.27</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>38.88</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>37.88</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>37.78</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>37.65</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>36.48</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>35.99</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>35.69</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="164">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>35.27</v>
+        <v>36.31</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>34.05</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="166">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>33.87</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="167">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>32.22</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>31.24</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="169">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>29.94</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="170">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>29.87</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>29.27</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>28.88</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>28.85</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>26.97</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,17 +9760,17 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>26.15</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>26.13</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>25.79</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>25.68</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>25.52</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,17 +10025,17 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>25.21</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>24.1</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>23.97</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>23.74</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="184">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>22.47</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="185">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>22.39</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>22.3</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="187">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701116 - KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="7" t="n">
-        <v>21.69</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="188">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955682 - KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="L188" s="5" t="n"/>
       <c r="M188" s="7" t="n">
-        <v>21.33</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="189">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
+          <t>SMRT-05900510-Los Angeles CA-020650072-KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="7" t="n">
-        <v>21.21</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="190">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437412 - KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="7" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="191">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437982 - KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="192">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955262 - KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="7" t="n">
-        <v>20.61</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="193">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650252 - KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="7" t="n">
-        <v>20.12</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="194">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>19.65</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="195">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>18.12</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="196">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955352-KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="7" t="n">
-        <v>17.89</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="197">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011114 - KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>17.57</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>15.77</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>15.35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,17 +11191,17 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>14.95</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,17 +11244,17 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>14.71</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="204">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
+          <t>SMRT-05900510-Los Angeles CA-020650132-KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="7" t="n">
-        <v>13.98</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="205">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649782 - KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="7" t="n">
-        <v>12.48</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="206">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650142 - KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="7" t="n">
-        <v>12.19</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="207">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650052 - KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="7" t="n">
-        <v>10.75</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="208">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>10.47</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="209">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>9.85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>7.74</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="216">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="217">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>5.81</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="218">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>5.53</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="219">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650242 - KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="7" t="n">
-        <v>4.49</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="220">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649342 - KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
@@ -12145,12 +12145,12 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="7" t="n">
-        <v>4.07</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="221">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="225">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="227">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="228">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12887,12 +12887,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,17 +13152,17 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955162 - KIT4M05563554WCW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955222 - KIT4M05563536BPJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650182 - KIT4M05413821GGW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955422 - KIT4M05563517BVR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955562 - KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,12 +13894,12 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 12:30 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 10:13 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 10:13 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 15:34 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2099.05</v>
+        <v>2113.57</v>
       </c>
     </row>
     <row r="3">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1332.43</v>
+        <v>1363.14</v>
       </c>
     </row>
     <row r="6">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>878.66</v>
+        <v>887.4299999999999</v>
       </c>
     </row>
     <row r="8">
@@ -993,7 +993,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>754.4</v>
+        <v>763.9</v>
       </c>
     </row>
     <row r="10">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>643.48</v>
+        <v>648.33</v>
       </c>
     </row>
     <row r="11">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>585.9299999999999</v>
+        <v>586.5599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>583.4400000000001</v>
+        <v>583.7</v>
       </c>
     </row>
     <row r="14">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>569.74</v>
+        <v>571.9299999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>518.0700000000001</v>
+        <v>518.22</v>
       </c>
     </row>
     <row r="16">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>500.45</v>
+        <v>504.24</v>
       </c>
     </row>
     <row r="18">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>496.26</v>
+        <v>500.45</v>
       </c>
     </row>
     <row r="19">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>475.35</v>
+        <v>477.6</v>
       </c>
     </row>
     <row r="21">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>473.96</v>
+        <v>475.84</v>
       </c>
     </row>
     <row r="22">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>450.18</v>
+        <v>450.49</v>
       </c>
     </row>
     <row r="24">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>428.89</v>
+        <v>430.3</v>
       </c>
     </row>
     <row r="25">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>410.85</v>
+        <v>411.34</v>
       </c>
     </row>
     <row r="27">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>410.4</v>
+        <v>410.41</v>
       </c>
     </row>
     <row r="28">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>408.48</v>
+        <v>409.72</v>
       </c>
     </row>
     <row r="29">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>341.85</v>
+        <v>349.13</v>
       </c>
     </row>
     <row r="31">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>321.84</v>
+        <v>322.69</v>
       </c>
     </row>
     <row r="32">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>313.55</v>
+        <v>313.77</v>
       </c>
     </row>
     <row r="33">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>298.99</v>
+        <v>301.23</v>
       </c>
     </row>
     <row r="34">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>298.15</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="35">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>297.09</v>
+        <v>298.74</v>
       </c>
     </row>
     <row r="36">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>272.98</v>
+        <v>273.78</v>
       </c>
     </row>
     <row r="37">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>266.95</v>
+        <v>267.29</v>
       </c>
     </row>
     <row r="39">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>257.01</v>
+        <v>258.41</v>
       </c>
     </row>
     <row r="40">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>249.72</v>
+        <v>251.47</v>
       </c>
     </row>
     <row r="42">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>198.69</v>
+        <v>199.31</v>
       </c>
     </row>
     <row r="46">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>198.15</v>
+        <v>198.88</v>
       </c>
     </row>
     <row r="47">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>196.77</v>
+        <v>197.74</v>
       </c>
     </row>
     <row r="48">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>187.68</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="49">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>182.67</v>
+        <v>182.69</v>
       </c>
     </row>
     <row r="50">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>172.83</v>
+        <v>174.58</v>
       </c>
     </row>
     <row r="52">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>172.31</v>
+        <v>174.02</v>
       </c>
     </row>
     <row r="53">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>168.97</v>
+        <v>170.1</v>
       </c>
     </row>
     <row r="54">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>144.89</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="57">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>143.33</v>
+        <v>143.61</v>
       </c>
     </row>
     <row r="58">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>137.76</v>
+        <v>139.82</v>
       </c>
     </row>
     <row r="59">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>131.31</v>
+        <v>131.59</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>130.94</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="63">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>130.43</v>
+        <v>130.72</v>
       </c>
     </row>
     <row r="64">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>129.82</v>
+        <v>130.55</v>
       </c>
     </row>
     <row r="65">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>127.35</v>
+        <v>127.38</v>
       </c>
     </row>
     <row r="66">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>120.74</v>
+        <v>120.81</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>119.92</v>
+        <v>120.11</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>119.07</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>117.68</v>
+        <v>119.79</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>117.09</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>115.85</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="74">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>114.3</v>
+        <v>114.81</v>
       </c>
     </row>
     <row r="75">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>110.34</v>
+        <v>110.35</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>106.48</v>
+        <v>109.38</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>104.51</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="79">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>104.21</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>101.98</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="81">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,17 +4937,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>98.03</v>
+        <v>98.69</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>97.44</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>95.48999999999999</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>93.22</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>92.09</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="89">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>91.5</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>91.20999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>89.7</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>85.23</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>82.18000000000001</v>
+        <v>84.04000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>81.95999999999999</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>81.72</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="100">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>77.84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>77.26000000000001</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="104">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>75.91</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="105">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>75.84</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="106">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,17 +6209,17 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,17 +6262,17 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>74.54000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>72.27</v>
+        <v>72.54000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>70.06</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="113">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>69.31999999999999</v>
+        <v>69.34999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>66.93000000000001</v>
+        <v>67.18000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>65.39</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>63.5</v>
+        <v>63.53</v>
       </c>
     </row>
     <row r="118">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>62.69</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="119">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>60.29</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="121">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>59.22</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="122">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>59.04</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="123">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>58.42</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="124">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>58.14</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="125">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>57.66</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="126">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>55.04</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="132">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>54.74</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>54.26</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>53.95</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>53.2</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>53.19</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>52.82</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>52.57</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>52.55</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>52.12</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>51.74</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>48.69</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>48.68</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>48.08</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>48.04</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>47.5</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="147">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>47.16</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>46.1</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="151">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>46.07</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="152">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>43.72</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="155">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>43.72</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="156">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>41.27</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="157">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>40.58</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="158">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>38.71</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="161">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>36.17</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="166">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>35.15</v>
+        <v>35.43</v>
       </c>
     </row>
     <row r="167">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>32.86</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="170">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>32.11</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="171">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>29.27</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>28.85</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="176">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>28.32</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>27.6</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="178">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>27.2</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="179">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>26.52</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="180">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>24.9</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>24.1</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="185">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649562 - KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="7" t="n">
-        <v>23.74</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="186">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438152 - KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="7" t="n">
-        <v>22.99</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="187">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>19.94</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="196">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>16</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="202">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>15.48</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="204">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="211">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>9.27</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="214">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>7.91</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="215">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>7.85</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="216">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649602 - KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="7" t="n">
-        <v>7.74</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="217">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649652 - KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="7" t="n">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="218">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="7" t="n">
-        <v>7.33</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="219">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701110 - KIT4M041546939GJ</t>
+          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C227" s="3" t="n">
@@ -12516,17 +12516,17 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="7" t="n">
-        <v>0.85</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="228">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - CW6892232 - KIT4P000832637V6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C228" s="3" t="n">
@@ -12569,17 +12569,17 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="7" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="229">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955442 - KIT4M05563503XXP</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
@@ -12622,17 +12622,17 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="7" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="230">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111112 - KIT4P000655962DJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
@@ -12675,17 +12675,17 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="7" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="231">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650092 - KIT4M05413830JN7</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
@@ -12728,17 +12728,17 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="7" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="232">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649222 - KIT4P00065640BFW</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12781,17 +12781,17 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="7" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="233">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="7" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="236">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955622 - KIT4M05563549RSR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="7" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="237">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,12 +13046,12 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="7" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,17 +13682,17 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>temp-05900510-KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,17 +13894,17 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 15:34 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 15:35 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 15:35 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 15:36 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 15:36 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 15:39 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 15:39 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 15:42 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 15:42 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 17:05 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 17:05 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 17:06 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2113.57</v>
+        <v>2140.2</v>
       </c>
     </row>
     <row r="3">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1363.14</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>887.4299999999999</v>
+        <v>896.01</v>
       </c>
     </row>
     <row r="8">
@@ -898,7 +898,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -909,12 +909,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>771.66</v>
+        <v>779.38</v>
       </c>
     </row>
     <row r="9">
@@ -951,7 +951,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437262 - KIT4P0008460369B</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437232 - KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -962,12 +962,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="7" t="n">
-        <v>763.9</v>
+        <v>771.66</v>
       </c>
     </row>
     <row r="10">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>648.33</v>
+        <v>652.58</v>
       </c>
     </row>
     <row r="11">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>586.5599999999999</v>
+        <v>588.77</v>
       </c>
     </row>
     <row r="13">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>583.7</v>
+        <v>585.03</v>
       </c>
     </row>
     <row r="14">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>571.9299999999999</v>
+        <v>578.52</v>
       </c>
     </row>
     <row r="15">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>518.22</v>
+        <v>519.2</v>
       </c>
     </row>
     <row r="16">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>504.24</v>
+        <v>512.46</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>480.85</v>
+        <v>482.26</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>477.6</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="21">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>475.84</v>
+        <v>478.98</v>
       </c>
     </row>
     <row r="22">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>450.49</v>
+        <v>453.29</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>430.3</v>
+        <v>439.55</v>
       </c>
     </row>
     <row r="25">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020650172 - KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>415.73</v>
+        <v>431.51</v>
       </c>
     </row>
     <row r="26">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>411.34</v>
+        <v>420.1</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>410.41</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="28">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>409.72</v>
+        <v>411.97</v>
       </c>
     </row>
     <row r="29">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>349.13</v>
+        <v>354.56</v>
       </c>
     </row>
     <row r="31">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>313.77</v>
+        <v>315.63</v>
       </c>
     </row>
     <row r="33">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>301.23</v>
+        <v>309.31</v>
       </c>
     </row>
     <row r="34">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>299.95</v>
+        <v>300.33</v>
       </c>
     </row>
     <row r="35">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>298.74</v>
+        <v>299.36</v>
       </c>
     </row>
     <row r="36">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>267.37</v>
+        <v>269.41</v>
       </c>
     </row>
     <row r="38">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>267.29</v>
+        <v>267.43</v>
       </c>
     </row>
     <row r="39">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955192 - KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="7" t="n">
-        <v>258.41</v>
+        <v>267.37</v>
       </c>
     </row>
     <row r="40">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437622 - KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>256.73</v>
+        <v>259.45</v>
       </c>
     </row>
     <row r="41">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438252 - KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>251.47</v>
+        <v>257.48</v>
       </c>
     </row>
     <row r="42">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>199.31</v>
+        <v>201.84</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>198.88</v>
+        <v>201.2</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>197.74</v>
+        <v>199.59</v>
       </c>
     </row>
     <row r="48">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>188.74</v>
+        <v>193.33</v>
       </c>
     </row>
     <row r="49">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>182.69</v>
+        <v>183.72</v>
       </c>
     </row>
     <row r="50">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>174.58</v>
+        <v>178.13</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>174.02</v>
+        <v>176.64</v>
       </c>
     </row>
     <row r="53">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>170.1</v>
+        <v>171.09</v>
       </c>
     </row>
     <row r="54">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>146.99</v>
+        <v>151.02</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650162 - KIT4M05413837SMB</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>145.5</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="57">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>143.61</v>
+        <v>145.79</v>
       </c>
     </row>
     <row r="58">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>139.82</v>
+        <v>140.79</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>132.39</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>131.59</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="61">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>131.31</v>
+        <v>132.08</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>131.04</v>
+        <v>131.78</v>
       </c>
     </row>
     <row r="63">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>130.72</v>
+        <v>131.46</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650192 - KIT4M054138007JF</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>130.55</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>127.38</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>126.03</v>
+        <v>128.03</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>123.21</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="68">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955482 - KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>120.81</v>
+        <v>125.27</v>
       </c>
     </row>
     <row r="69">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>120.11</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="70">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>119.92</v>
+        <v>122.45</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649472-KIT4M05413795QHK</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>119.79</v>
+        <v>120.86</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>117.29</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="73">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>117.13</v>
+        <v>118.72</v>
       </c>
     </row>
     <row r="74">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>114.81</v>
+        <v>117.35</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>113.25</v>
+        <v>116.39</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>110.35</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="77">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955572 - KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>109.38</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,17 +4619,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>106.48</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>105.3</v>
+        <v>109.31</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>104.62</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>101.97</v>
+        <v>106.33</v>
       </c>
     </row>
     <row r="82">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>100.93</v>
+        <v>104.76</v>
       </c>
     </row>
     <row r="83">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649822 - KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>104.74</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,17 +4937,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>98.69</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>98.25</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>97.44</v>
+        <v>99.55</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>96</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>93.22</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>91.65000000000001</v>
+        <v>93.51000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955382 - KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>91.20999999999999</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="91">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649422 - KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,17 +5361,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>87.73</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="95">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>85.20999999999999</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>84.04000000000001</v>
+        <v>86.15000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>82.18000000000001</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="99">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011118 - KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="7" t="n">
-        <v>81.84</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>79.44</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="101">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>79.13</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>78</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>77.84</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>76.44</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="105">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>75.94</v>
+        <v>77.18000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>75.81</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>74.76000000000001</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955692 - KIT4M05563579H9F</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>72.54000000000001</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="111">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>70.47</v>
+        <v>71.26000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>69.34999999999999</v>
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>67.18000000000001</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>65.45999999999999</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>64.33</v>
+        <v>66.59</v>
       </c>
     </row>
     <row r="117">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649952 - KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L117" s="5" t="n"/>
       <c r="M117" s="7" t="n">
-        <v>63.53</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="118">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>63.49</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="119">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>60.48</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>60.31</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>59.38</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="123">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>58.61</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="124">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>58.27</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="125">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>57.67</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>57.22</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>56.5</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,17 +7269,17 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>56.35</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>55.94</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>55.64</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>55.05</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>54.83</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>54.77</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>54.26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>53.95</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>53.34</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>53.2</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="138">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482704 - KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>52.59</v>
+        <v>53.21</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>52.57</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>52.54</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="141">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>49.07</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="143">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>48.69</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="144">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>48.6</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="145">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>48.09</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="146">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>48.04</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>47.38</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>47.19</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="150">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955652 - KIT4M0556358988Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649622 - KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="7" t="n">
-        <v>46.87</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="151">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>44.19</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>43.95</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>43.73</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="156">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649302 - KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>41.54</v>
+        <v>44.09</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>40.59</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>39.41</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>38.88</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>38.74</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>38.62</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="162">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>36.48</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>36.31</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>36.26</v>
+        <v>36.31</v>
       </c>
     </row>
     <row r="166">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>35.43</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>34.1</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>34.05</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>32.88</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="170">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>32.12</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="171">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>29.87</v>
+        <v>30.64</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>29.83</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>29.38</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>29.27</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>29.05</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="177">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>27.21</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="179">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>26.53</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="180">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>25.79</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>25.7</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="183">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>24.97</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="184">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>24.29</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="185">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
+          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>20.12</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="195">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649462-KIT4M05413796V9K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955212 - KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="7" t="n">
-        <v>20.07</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="196">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>17.99</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="198">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>16.24</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="202">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -11191,17 +11191,17 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>15.77</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="203">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020426432 - KIT4P00066070HN4</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482706 - KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
@@ -11244,17 +11244,17 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="7" t="n">
-        <v>15.64</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="204">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>10.07</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="210">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>10.04</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="211">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>9.859999999999999</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="212">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>9.380000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>9.27</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="214">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438272 - KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="7" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="215">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438212 - KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="7" t="n">
-        <v>7.92</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="226">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,17 +13046,17 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438202 - KIT4M05872506TTB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>temp-05900510-KIT4M041546939GJ</t>
+          <t>SMS - 05900510 - Los Angeles CA - CW6978120 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14477,12 +14477,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437382 - KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437752 - KIT4M05872577TWT</t>
+          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
@@ -16703,12 +16703,12 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649582 - KIT4M05413774JZX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437522 - KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
@@ -16809,12 +16809,12 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
@@ -16862,12 +16862,12 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437452 - KIT4M05872580C6X</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
@@ -16915,12 +16915,12 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649362 - KIT4M05368336DBC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649332 - KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437482-KIT4M05872578G7Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437572 - KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
@@ -17127,12 +17127,12 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
@@ -17180,12 +17180,12 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
@@ -17233,12 +17233,12 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491802BZV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
@@ -17286,12 +17286,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491803672</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
@@ -17339,12 +17339,12 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491805F7Z</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491799CRP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
@@ -17551,12 +17551,12 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491795MWG</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
@@ -17869,12 +17869,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491820X58</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
@@ -17922,12 +17922,12 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491813KGS</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491812JDV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491808P4F</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
@@ -18399,12 +18399,12 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491809ZR6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491797NCX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
@@ -18505,12 +18505,12 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918068FF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
@@ -18823,12 +18823,12 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918346DB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491828XWF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
@@ -18982,12 +18982,12 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491837DPX</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491829CD2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491830G2J</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918322GZ</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -19424,7 +19424,7 @@
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21 17:06 by build_starlink_usage.py</t>
+          <t>Generated 2026-09-21 21:39 by build_starlink_usage.py</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Current_by_Kit.xlsx
+++ b/Starlink_Usage_Current_by_Kit.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="7" t="n">
-        <v>2140.2</v>
+        <v>2184.28</v>
       </c>
     </row>
     <row r="3">
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="7" t="n">
-        <v>1399</v>
+        <v>1469.32</v>
       </c>
     </row>
     <row r="6">
@@ -887,7 +887,7 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="7" t="n">
-        <v>896.01</v>
+        <v>921.52</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +940,7 @@
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="7" t="n">
-        <v>779.38</v>
+        <v>839.87</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="7" t="n">
-        <v>652.58</v>
+        <v>676.47</v>
       </c>
     </row>
     <row r="11">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="7" t="n">
-        <v>588.77</v>
+        <v>592.1</v>
       </c>
     </row>
     <row r="13">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="7" t="n">
-        <v>585.03</v>
+        <v>586.64</v>
       </c>
     </row>
     <row r="14">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="7" t="n">
-        <v>578.52</v>
+        <v>581.29</v>
       </c>
     </row>
     <row r="15">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="7" t="n">
-        <v>519.2</v>
+        <v>532.12</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955372-KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="7" t="n">
-        <v>513.88</v>
+        <v>526.3</v>
       </c>
     </row>
     <row r="17">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437272 - KIT4P0008459589D</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438232 - KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1386,17 +1386,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="7" t="n">
-        <v>512.46</v>
+        <v>513.88</v>
       </c>
     </row>
     <row r="18">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="7" t="n">
-        <v>500.45</v>
+        <v>512.21</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649202 - KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1492,17 +1492,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="7" t="n">
-        <v>482.26</v>
+        <v>500.45</v>
       </c>
     </row>
     <row r="20">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955522 - KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="7" t="n">
-        <v>480.85</v>
+        <v>493.34</v>
       </c>
     </row>
     <row r="21">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="7" t="n">
-        <v>478.98</v>
+        <v>481.33</v>
       </c>
     </row>
     <row r="22">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955052 - KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="7" t="n">
-        <v>466.53</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="23">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649242 - KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="7" t="n">
-        <v>453.29</v>
+        <v>466.53</v>
       </c>
     </row>
     <row r="24">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955102 - KIT4P000739257CR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955112 - KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="7" t="n">
-        <v>439.55</v>
+        <v>459.82</v>
       </c>
     </row>
     <row r="25">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="7" t="n">
-        <v>431.51</v>
+        <v>442.6</v>
       </c>
     </row>
     <row r="26">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="7" t="n">
-        <v>420.1</v>
+        <v>436.67</v>
       </c>
     </row>
     <row r="27">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="7" t="n">
-        <v>415.73</v>
+        <v>419.61</v>
       </c>
     </row>
     <row r="28">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650102 - KIT4M054138257Z7</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649262 - KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="7" t="n">
-        <v>411.97</v>
+        <v>415.73</v>
       </c>
     </row>
     <row r="29">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="7" t="n">
-        <v>354.56</v>
+        <v>372.44</v>
       </c>
     </row>
     <row r="31">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="7" t="n">
-        <v>322.69</v>
+        <v>328.15</v>
       </c>
     </row>
     <row r="32">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955132 - KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="7" t="n">
-        <v>315.63</v>
+        <v>324.92</v>
       </c>
     </row>
     <row r="33">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649442 - KIT4M054137885SM</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011116 - KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="7" t="n">
-        <v>309.31</v>
+        <v>316.07</v>
       </c>
     </row>
     <row r="34">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="7" t="n">
-        <v>300.33</v>
+        <v>304.71</v>
       </c>
     </row>
     <row r="35">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="7" t="n">
-        <v>299.36</v>
+        <v>301.88</v>
       </c>
     </row>
     <row r="36">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="7" t="n">
-        <v>273.78</v>
+        <v>290.91</v>
       </c>
     </row>
     <row r="37">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955072 - KIT4P0007258645B</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955342 - KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="7" t="n">
-        <v>269.41</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="38">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="7" t="n">
-        <v>267.43</v>
+        <v>267.96</v>
       </c>
     </row>
     <row r="39">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="7" t="n">
-        <v>259.45</v>
+        <v>263.81</v>
       </c>
     </row>
     <row r="41">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="7" t="n">
-        <v>257.48</v>
+        <v>257.93</v>
       </c>
     </row>
     <row r="42">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="7" t="n">
-        <v>201.84</v>
+        <v>208.19</v>
       </c>
     </row>
     <row r="46">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955662 - KIT4M05563574ZBN</t>
+          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="7" t="n">
-        <v>201.2</v>
+        <v>204.08</v>
       </c>
     </row>
     <row r="47">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437422 - KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="7" t="n">
-        <v>199.59</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6858375 - KIT4M05872512N5W</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955292 - KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="7" t="n">
-        <v>193.33</v>
+        <v>202.75</v>
       </c>
     </row>
     <row r="49">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="7" t="n">
-        <v>183.72</v>
+        <v>185.54</v>
       </c>
     </row>
     <row r="50">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="7" t="n">
-        <v>180.28</v>
+        <v>184.22</v>
       </c>
     </row>
     <row r="51">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649282 - KIT4M05368213974</t>
+          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="7" t="n">
-        <v>178.13</v>
+        <v>183.45</v>
       </c>
     </row>
     <row r="52">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 -  Los Angeles CA - 020649512 - KIT4M054138318Q7</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649752 - KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="7" t="n">
-        <v>176.64</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="53">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="7" t="n">
-        <v>171.09</v>
+        <v>178.8</v>
       </c>
     </row>
     <row r="54">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="7" t="n">
-        <v>151.02</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="56">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="7" t="n">
-        <v>147.1</v>
+        <v>148.73</v>
       </c>
     </row>
     <row r="57">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955462 - KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="7" t="n">
-        <v>145.79</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="58">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437992 -  KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="7" t="n">
-        <v>140.79</v>
+        <v>147.61</v>
       </c>
     </row>
     <row r="59">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649862 - KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="7" t="n">
-        <v>137.09</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="60">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955552 - KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="7" t="n">
-        <v>132.39</v>
+        <v>140.59</v>
       </c>
     </row>
     <row r="61">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="7" t="n">
-        <v>132.08</v>
+        <v>139.16</v>
       </c>
     </row>
     <row r="62">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="7" t="n">
-        <v>131.78</v>
+        <v>134.45</v>
       </c>
     </row>
     <row r="63">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="7" t="n">
-        <v>131.46</v>
+        <v>133.95</v>
       </c>
     </row>
     <row r="64">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955272 - KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="7" t="n">
-        <v>131.31</v>
+        <v>133.43</v>
       </c>
     </row>
     <row r="65">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437582 - KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="7" t="n">
-        <v>131.04</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="66">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
+          <t>SMRT-05900510-Los Angeles CA-020649522-KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="7" t="n">
-        <v>128.03</v>
+        <v>131.31</v>
       </c>
     </row>
     <row r="67">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
+          <t>SS - 05900510 - Los Angeles, CA  - 020649572 - KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="7" t="n">
-        <v>126.03</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="68">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="7" t="n">
-        <v>125.27</v>
+        <v>129.58</v>
       </c>
     </row>
     <row r="69">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649732 - KIT4M046047467T4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955182 - KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="7" t="n">
-        <v>124.24</v>
+        <v>129.24</v>
       </c>
     </row>
     <row r="70">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="7" t="n">
-        <v>122.45</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="71">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649852 - KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="7" t="n">
-        <v>120.86</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="72">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="7" t="n">
-        <v>119.92</v>
+        <v>123.68</v>
       </c>
     </row>
     <row r="73">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649382 - KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="7" t="n">
-        <v>118.72</v>
+        <v>123.06</v>
       </c>
     </row>
     <row r="74">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650002 - KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="7" t="n">
-        <v>117.35</v>
+        <v>119.92</v>
       </c>
     </row>
     <row r="75">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649842 - KIT4M025787739XF</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650212 - KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="7" t="n">
-        <v>116.39</v>
+        <v>119.87</v>
       </c>
     </row>
     <row r="76">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437402 - KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="7" t="n">
-        <v>113.25</v>
+        <v>119.12</v>
       </c>
     </row>
     <row r="77">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="7" t="n">
-        <v>112.96</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="78">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111114 - KIT4P00065593VWC</t>
+          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4619,17 +4619,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="7" t="n">
-        <v>112.9</v>
+        <v>114.07</v>
       </c>
     </row>
     <row r="79">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles, CA - 020955232 - KIT4M05563538RZV</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649322 - KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="7" t="n">
-        <v>109.31</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="80">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="7" t="n">
-        <v>106.48</v>
+        <v>109.82</v>
       </c>
     </row>
     <row r="81">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955252 - KIT4M05563584FVC</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="7" t="n">
-        <v>106.33</v>
+        <v>106.72</v>
       </c>
     </row>
     <row r="82">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955322 - KIT4M055635305RS</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955432 - KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="7" t="n">
-        <v>104.76</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="83">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="7" t="n">
-        <v>104.74</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="84">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="7" t="n">
-        <v>100.93</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="85">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="7" t="n">
-        <v>99.90000000000001</v>
+        <v>101.39</v>
       </c>
     </row>
     <row r="86">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438222 - KIT4M058725299QP</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827018 - KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="7" t="n">
-        <v>99.55</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="87">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649392 - KIT4M05368206BZP</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="7" t="n">
-        <v>98.95999999999999</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="7" t="n">
-        <v>97.44</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021438182 - KIT4M05872528P9D</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="7" t="n">
-        <v>93.51000000000001</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="90">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="7" t="n">
-        <v>93.22</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="91">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="7" t="n">
-        <v>92.13</v>
+        <v>92.27</v>
       </c>
     </row>
     <row r="92">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="7" t="n">
-        <v>89.79000000000001</v>
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="7" t="n">
-        <v>89.48999999999999</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="94">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649762 - KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="7" t="n">
-        <v>87.73</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649772 - KIT4M04475152RGR</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955092 - KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -5520,17 +5520,17 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="7" t="n">
-        <v>86.92</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649452 - KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="7" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="97">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649682 - KIT4M046047384RX</t>
+          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="7" t="n">
-        <v>86.15000000000001</v>
+        <v>87.64</v>
       </c>
     </row>
     <row r="98">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 021437562 - KIT4M05872583P58</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437592 - KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="7" t="n">
-        <v>85.11</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="7" t="n">
-        <v>79.67</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="101">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955172-KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="7" t="n">
-        <v>79.63</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="102">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="7" t="n">
-        <v>79.44</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649672 - KIT4M04606113TPB</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649902 - KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="7" t="n">
-        <v>78.52</v>
+        <v>79.81</v>
       </c>
     </row>
     <row r="104">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438072 - KIT4M057996885ZV</t>
+          <t>STS - 05900510 - Los Angeles, CA - 0204827011112 - KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="7" t="n">
-        <v>77.84</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="105">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="7" t="n">
-        <v>77.18000000000001</v>
+        <v>78.01000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="7" t="n">
-        <v>75.94</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="107">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270114 - KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="7" t="n">
-        <v>75.81</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="108">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
+          <t>SSC - 05900510 -  Los Angeles CA - 021437862 - KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="7" t="n">
-        <v>74.76000000000001</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="109">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -6262,17 +6262,17 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>75.18000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649612 - KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="7" t="n">
-        <v>73.63</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955032 - KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="7" t="n">
-        <v>71.38</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020955312 - KIT4M0556351956H</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="7" t="n">
-        <v>71.26000000000001</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="113">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955712 - KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="7" t="n">
-        <v>69.48999999999999</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="114">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437832 - KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="7" t="n">
-        <v>67.29000000000001</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="115">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827016 - KIT4M041536494G6</t>
+          <t>SSC - 05900510 - Los Angeles CA - 021437792 - KIT4M05872507528</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="7" t="n">
-        <v>67.09</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="116">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955642 - KIT4M05563573WKC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649372 - KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="7" t="n">
-        <v>66.59</v>
+        <v>67.34</v>
       </c>
     </row>
     <row r="117">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="7" t="n">
-        <v>63.6</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="119">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020650012 - KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="7" t="n">
-        <v>62.58</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="120">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438282 - KIT4M05872508VTN</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="7" t="n">
-        <v>61.91</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="121">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437902 - KIT4M05799717WZV</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111110 - KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="7" t="n">
-        <v>60.66</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="122">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="7" t="n">
-        <v>60.31</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="123">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="L123" s="5" t="n"/>
       <c r="M123" s="7" t="n">
-        <v>58.84</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="124">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438262 - KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="7" t="n">
-        <v>58.62</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="125">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955632 - KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="7" t="n">
-        <v>58.62</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="126">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955702 - KIT4M05563571G8W</t>
+          <t>SS - 05900510 -  Los Angeles CA - 020955242 - KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="7" t="n">
-        <v>58.57</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="127">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="L127" s="5" t="n"/>
       <c r="M127" s="7" t="n">
-        <v>58.05</v>
+        <v>59.69</v>
       </c>
     </row>
     <row r="128">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
+          <t>SMRT-05900510-Los Angeles, CA-020955582-KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -7269,17 +7269,17 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>57.22</v>
+        <v>59.35</v>
       </c>
     </row>
     <row r="129">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437782 - KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="7" t="n">
-        <v>56.5</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="130">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="7" t="n">
-        <v>56.35</v>
+        <v>58.42</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="7" t="n">
-        <v>56.07</v>
+        <v>58.16</v>
       </c>
     </row>
     <row r="132">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438242 - KIT4M058725094XP</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649212 - KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -7481,17 +7481,17 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="7" t="n">
-        <v>55.54</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="133">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649492 - KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="7" t="n">
-        <v>55.05</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="134">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649962 - KIT4M05413783PFQ</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701118 - KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="7" t="n">
-        <v>55</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="135">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649892 - KIT4M05413777DGG</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955392 - KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="7" t="n">
-        <v>54.3</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="136">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
+          <t>SMRT-05900510-Los Angeles CA-020649312-KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="7" t="n">
-        <v>53.95</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="137">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827010 - KIT4M046047372KJ</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438192 - KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="7" t="n">
-        <v>53.36</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="138">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="7" t="n">
-        <v>53.21</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="139">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="7" t="n">
-        <v>52.66</v>
+        <v>53.05</v>
       </c>
     </row>
     <row r="140">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270116 - KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="7" t="n">
-        <v>52.57</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="141">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="7" t="n">
-        <v>52.12</v>
+        <v>52.57</v>
       </c>
     </row>
     <row r="142">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955282 - KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="7" t="n">
-        <v>50.49</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="143">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="7" t="n">
-        <v>50.3</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="144">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020955512 - KIT4M055635779MM</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649272 - KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="7" t="n">
-        <v>49.55</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="145">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649642 - KIT4M05413826Z6Z</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955472 - KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="7" t="n">
-        <v>49.42</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="146">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="7" t="n">
-        <v>49.33</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="147">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
+          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="7" t="n">
-        <v>48.04</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="148">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650232 - KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="7" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="149">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - CW6578840- KIT4M04475128THH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650112 - KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="7" t="n">
-        <v>47.5</v>
+        <v>47.99</v>
       </c>
     </row>
     <row r="150">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="7" t="n">
-        <v>46.1</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="152">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="7" t="n">
-        <v>45.68</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="153">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955142 - KIT4M05563518ZJD</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270112 - KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="7" t="n">
-        <v>44.52</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="154">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
+          <t>SMRT-05900510-Los Angeles CA-020650202-KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="7" t="n">
-        <v>44.33</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="155">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020650152 - KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="7" t="n">
-        <v>44.19</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="156">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="7" t="n">
-        <v>44.09</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="157">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649812 - KIT4M04604742S6S</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="7" t="n">
-        <v>43.42</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="158">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="7" t="n">
-        <v>39.46</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="159">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="7" t="n">
-        <v>39.41</v>
+        <v>40.27</v>
       </c>
     </row>
     <row r="160">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649832 - KIT4M03866596RZG</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955672 - KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="7" t="n">
-        <v>38.91</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="161">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955412 - KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="7" t="n">
-        <v>38.88</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="162">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="7" t="n">
-        <v>37.65</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="163">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020955152 - KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="7" t="n">
-        <v>36.59</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="164">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649932 - KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="7" t="n">
-        <v>36.48</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="165">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649712 - KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="7" t="n">
-        <v>36.31</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="166">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437612 - KIT4M058725265DP</t>
+          <t>STS - 05900510 - Los Angeles CA - 020650082 - KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="7" t="n">
-        <v>35.44</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="167">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020955302 - KIT4M055635158PC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="7" t="n">
-        <v>35.16</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="168">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650042 - KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="7" t="n">
-        <v>34.1</v>
+        <v>36.31</v>
       </c>
     </row>
     <row r="169">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
+          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="7" t="n">
-        <v>34.05</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="170">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955362 - KIT4M05563528MKX</t>
+          <t>SMRT-05900510-LOS ANGELES CA-020955202-KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="7" t="n">
-        <v>32.72</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="171">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
+          <t xml:space="preserve">SS - 05900510 - Los Angeles, CA - 020649552 - KIT4M05413835RPF </t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="7" t="n">
-        <v>31.24</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="172">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437392 - KIT4M05872555BJR</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="7" t="n">
-        <v>30.64</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="173">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="7" t="n">
-        <v>30.08</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="174">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649412 - KIT4M05413769796</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="7" t="n">
-        <v>30.03</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="175">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482702 - KIT4M04604743HSS</t>
+          <t>SMRT-05900510-Los Angeles CA-020649292-KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="7" t="n">
-        <v>29.83</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="176">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437552 - KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="7" t="n">
-        <v>29.27</v>
+        <v>30.11</v>
       </c>
     </row>
     <row r="177">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650262 - KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="7" t="n">
-        <v>28.85</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="178">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270110 - KIT4M038677586ZX</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="7" t="n">
-        <v>28.46</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="179">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649352 - KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="7" t="n">
-        <v>26.96</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="180">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
+          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -10025,17 +10025,17 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="7" t="n">
-        <v>26.15</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="181">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437892 - KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="7" t="n">
-        <v>26.01</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="182">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955542 - KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="7" t="n">
-        <v>25.79</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="183">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 020649912 - KIT4M05413836KJC</t>
+          <t>STS - 05900510 - Los Angeles CA - 02048270111116 - KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -10184,17 +10184,17 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="7" t="n">
-        <v>25.34</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="184">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438172 - KIT4M05872500684</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649402 - KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="7" t="n">
-        <v>25.24</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="185">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="7" t="n">
-        <v>20.13</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="195">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="7" t="n">
-        <v>18.47</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="198">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="7" t="n">
-        <v>17.57</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="199">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020649532 - KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="7" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="200">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649982 - KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="7" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="201">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955332 - KIT4M05563590ZFQ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649702 - KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="7" t="n">
-        <v>16.45</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="202">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="7" t="n">
-        <v>15.81</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="203">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="7" t="n">
-        <v>10.75</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="209">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827014 - KIT4M04475149XG5</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="7" t="n">
-        <v>10.4</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="210">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955492 - KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="7" t="n">
-        <v>10.08</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="211">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="7" t="n">
-        <v>10.07</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="212">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020482701112 - KIT4M04158973M2C</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649502 - KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="7" t="n">
-        <v>9.869999999999999</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="213">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955602 - KIT4M05563560225</t>
+          <t>STS - 05900510 - Los Angeles CA - 020482708 - KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="7" t="n">
-        <v>9.67</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="214">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C224" s="3" t="n">
@@ -12357,12 +12357,12 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="7" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="225">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020649662 - KIT4M05413772977</t>
         </is>
       </c>
       <c r="C225" s="3" t="n">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="7" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="226">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491818QD2</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649922 - KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C226" s="3" t="n">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="7" t="n">
-        <v>0.98</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="227">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
@@ -12781,12 +12781,12 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 020650022 - KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649942 - KIT4M05413786BXC</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955402 - KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
@@ -12887,12 +12887,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
+          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438102 - KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
@@ -13046,17 +13046,17 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 020649872 - KIT4M054138175VJ</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437242 - KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
+          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
+          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
+          <t>SMS - 05900510 - Los Angeles CA - CW6978120 - KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
+          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
@@ -13682,17 +13682,17 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4P00073922FPF</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>814641</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>G3 HPERF</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - CW6978120 - KIT4M041546939GJ</t>
+          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955122 - KIT4P00073922FPF</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437922 - KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
@@ -13894,17 +13894,17 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073922FPF</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>814641</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>G3 HPERF</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 0204827011110 - KIT4M03866627GHD</t>
+          <t>SS  - 05900510 - Los Angeles CA - 020650222 - KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA -021437942 - KIT4M05799709G5Q</t>
+          <t>SS - 05900510 - Los Angeles CA - 6862083  - KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020649972 - KIT4M05413791FK5</t>
+          <t>SS - 05900510 - Los Angeles CA - 020650062 - KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 020649482 - KIT4M054137938P7</t>
+          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>STS - 05900510 - Los Angeles CA - 020649882 - KIT4M054137997HR</t>
+          <t>SMRT-05900510-Los Angeles CA-020650032-KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 020955612 - KIT4M0556355588P</t>
+          <t>SS - 05900510 - Los Angeles, CA - 020649992 - KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021438052 - KIT4M05872522W7W</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437692 - KIT4M05872518P78</t>
+          <t>SS - 05900510 - Los Angeles CA - 021438292 - KIt4m058725108K2</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437702 - KIT4M05872515PJT</t>
+          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
@@ -14477,12 +14477,12 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437722 - KIT4M05872498PP4</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437432 - KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437322 - KIT4M05872567V72</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437472 - KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437462 - KIT4M05872575BC8</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437762 - KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437362 - KIT4M05872574NKX</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -14742,12 +14742,12 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437852 - KIT4M0587257292W</t>
+          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437302 - KIT4M05872571T4K</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437712-KIT4M05872570FCC</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437312 - KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -14901,12 +14901,12 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437502 - KIT4M058725695CN</t>
+          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
+          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437602 - KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
@@ -15060,12 +15060,12 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437532 - KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437342 - KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles, CA - 021437772 - KIT4M05872563FWB</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437512 - KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
+          <t>SMA - 05900510 - Los Angeles CA - 021437492 - KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437882-KIT4M05872527QK6</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437662 - KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437822-KIT4M0587253378R</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437952 - KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437742 - KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
+          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>SMRT-05900510-Los Angeles CA-021437352-KIT4M05872545Q8H</t>
+          <t>SS - 05900510 -  Los Angeles CA - 021437682 - KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
+          <t>SMRT-05900510-Los Angeles CA-021437842-KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437372 - KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437542 - KIT4M05872553WFR</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437652 - KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437332 - KIT4M05872554RHM</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437912 - KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917936NF</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917925MB</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M064917914G5</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491790945</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
@@ -16120,12 +16120,12 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491789PJ6</t>
+          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>SMTS - 05900510 - Los Angeles CA - 6851959 - KIT4M06491786BS9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437972 - KIT4M06490327GMP</t>
+          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>SMS - 05900510 - Los Angeles CA - 021437872 - KIT4M06490319DDN</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
+          <t>SS - 05900510 - Los Angeles CA  - 020649432 - KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437642 - KIT4M05872590N8X</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>SS - 05900510 - Los Angeles CA - 021437802 - KIT4M05872589TM9</t>
+          <t>SS - 05900510 - Los Angeles CA - 021437442 - KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B304" s="2" t=